--- a/docs/qa/real-source-2026-10/real-source-test.xlsx
+++ b/docs/qa/real-source-2026-10/real-source-test.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answers" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings verdict" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="After fixes" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -495,7 +496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Real-source ingestion test (spec 0006)</t>
+          <t>Real-source ingestion test (spec 0006), re-run after the spec 0007 fixes (A1)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -605,15 +606,15 @@
         </is>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A5,Retrieval!$B$2:$B$251,C5,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A5,Retrieval!$B$2:$B$305,C5,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A5,Retrieval!$B$2:$B$251,C5,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A5,Retrieval!$B$2:$B$305,C5,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A5,Retrieval!$B$2:$B$251,C5,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A5,Retrieval!$B$2:$B$305,C5,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G5" s="5">
@@ -650,15 +651,15 @@
         </is>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A6,Retrieval!$B$2:$B$251,C6,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A6,Retrieval!$B$2:$B$305,C6,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A6,Retrieval!$B$2:$B$251,C6,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A6,Retrieval!$B$2:$B$305,C6,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A6,Retrieval!$B$2:$B$251,C6,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A6,Retrieval!$B$2:$B$305,C6,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -695,15 +696,15 @@
         </is>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A7,Retrieval!$B$2:$B$251,C7,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A7,Retrieval!$B$2:$B$305,C7,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A7,Retrieval!$B$2:$B$251,C7,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A7,Retrieval!$B$2:$B$305,C7,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A7,Retrieval!$B$2:$B$251,C7,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A7,Retrieval!$B$2:$B$305,C7,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -740,15 +741,15 @@
         </is>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A8,Retrieval!$B$2:$B$251,C8,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A8,Retrieval!$B$2:$B$305,C8,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A8,Retrieval!$B$2:$B$251,C8,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A8,Retrieval!$B$2:$B$305,C8,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A8,Retrieval!$B$2:$B$251,C8,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A8,Retrieval!$B$2:$B$305,C8,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G8" s="5">
@@ -785,15 +786,15 @@
         </is>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A9,Retrieval!$B$2:$B$251,C9,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A9,Retrieval!$B$2:$B$305,C9,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A9,Retrieval!$B$2:$B$251,C9,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A9,Retrieval!$B$2:$B$305,C9,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A9,Retrieval!$B$2:$B$251,C9,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A9,Retrieval!$B$2:$B$305,C9,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G9" s="5">
@@ -830,15 +831,15 @@
         </is>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A10,Retrieval!$B$2:$B$251,C10,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A10,Retrieval!$B$2:$B$305,C10,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A10,Retrieval!$B$2:$B$251,C10,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A10,Retrieval!$B$2:$B$305,C10,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A10,Retrieval!$B$2:$B$251,C10,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A10,Retrieval!$B$2:$B$305,C10,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G10" s="5">
@@ -875,15 +876,15 @@
         </is>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A11,Retrieval!$B$2:$B$251,C11,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A11,Retrieval!$B$2:$B$305,C11,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A11,Retrieval!$B$2:$B$251,C11,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A11,Retrieval!$B$2:$B$305,C11,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A11,Retrieval!$B$2:$B$251,C11,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A11,Retrieval!$B$2:$B$305,C11,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G11" s="5">
@@ -920,15 +921,15 @@
         </is>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A12,Retrieval!$B$2:$B$251,C12,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A12,Retrieval!$B$2:$B$305,C12,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A12,Retrieval!$B$2:$B$251,C12,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A12,Retrieval!$B$2:$B$305,C12,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A12,Retrieval!$B$2:$B$251,C12,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A12,Retrieval!$B$2:$B$305,C12,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -965,15 +966,15 @@
         </is>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A13,Retrieval!$B$2:$B$251,C13,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A13,Retrieval!$B$2:$B$305,C13,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A13,Retrieval!$B$2:$B$251,C13,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A13,Retrieval!$B$2:$B$305,C13,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A13,Retrieval!$B$2:$B$251,C13,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A13,Retrieval!$B$2:$B$305,C13,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -1010,15 +1011,15 @@
         </is>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A14,Retrieval!$B$2:$B$251,C14,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A14,Retrieval!$B$2:$B$305,C14,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A14,Retrieval!$B$2:$B$251,C14,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A14,Retrieval!$B$2:$B$305,C14,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A14,Retrieval!$B$2:$B$251,C14,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A14,Retrieval!$B$2:$B$305,C14,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -1055,15 +1056,15 @@
         </is>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A15,Retrieval!$B$2:$B$251,C15,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A15,Retrieval!$B$2:$B$305,C15,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A15,Retrieval!$B$2:$B$251,C15,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A15,Retrieval!$B$2:$B$305,C15,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A15,Retrieval!$B$2:$B$251,C15,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A15,Retrieval!$B$2:$B$305,C15,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -1100,15 +1101,15 @@
         </is>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A16,Retrieval!$B$2:$B$251,C16,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A16,Retrieval!$B$2:$B$305,C16,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A16,Retrieval!$B$2:$B$251,C16,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A16,Retrieval!$B$2:$B$305,C16,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A16,Retrieval!$B$2:$B$251,C16,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A16,Retrieval!$B$2:$B$305,C16,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -1131,29 +1132,29 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Recommended settings (v2)</t>
+          <t>After fixes: recommended (v3)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A17,Retrieval!$B$2:$B$251,C17,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A17,Retrieval!$B$2:$B$305,C17,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A17,Retrieval!$B$2:$B$251,C17,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A17,Retrieval!$B$2:$B$305,C17,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A17,Retrieval!$B$2:$B$251,C17,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A17,Retrieval!$B$2:$B$305,C17,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -1176,29 +1177,29 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Recommended settings (v2)</t>
+          <t>After fixes: recommended (v3)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="D18" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A18,Retrieval!$B$2:$B$251,C18,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A18,Retrieval!$B$2:$B$305,C18,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E18" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A18,Retrieval!$B$2:$B$251,C18,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A18,Retrieval!$B$2:$B$305,C18,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F18" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A18,Retrieval!$B$2:$B$251,C18,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A18,Retrieval!$B$2:$B$305,C18,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -1221,29 +1222,29 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Recommended settings (v2)</t>
+          <t>After fixes: recommended (v3)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="D19" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A19,Retrieval!$B$2:$B$251,C19,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A19,Retrieval!$B$2:$B$305,C19,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E19" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A19,Retrieval!$B$2:$B$251,C19,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A19,Retrieval!$B$2:$B$305,C19,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F19" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A19,Retrieval!$B$2:$B$251,C19,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A19,Retrieval!$B$2:$B$305,C19,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -1266,29 +1267,29 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>R1w</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Recommended, publish others with warnings</t>
+          <t>After fixes: recommended (v3)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="D20" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A20,Retrieval!$B$2:$B$251,C20,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A20,Retrieval!$B$2:$B$305,C20,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E20" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A20,Retrieval!$B$2:$B$251,C20,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A20,Retrieval!$B$2:$B$305,C20,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F20" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A20,Retrieval!$B$2:$B$251,C20,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A20,Retrieval!$B$2:$B$305,C20,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -1311,29 +1312,29 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>R1w</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Recommended, publish others with warnings</t>
+          <t>Recommended settings (v2)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D21" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A21,Retrieval!$B$2:$B$251,C21,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A21,Retrieval!$B$2:$B$305,C21,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E21" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A21,Retrieval!$B$2:$B$251,C21,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A21,Retrieval!$B$2:$B$305,C21,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F21" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A21,Retrieval!$B$2:$B$251,C21,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A21,Retrieval!$B$2:$B$305,C21,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -1356,29 +1357,29 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>R1w</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Recommended, publish others with warnings</t>
+          <t>Recommended settings (v2)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="D22" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A22,Retrieval!$B$2:$B$251,C22,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A22,Retrieval!$B$2:$B$305,C22,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E22" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A22,Retrieval!$B$2:$B$251,C22,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A22,Retrieval!$B$2:$B$305,C22,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F22" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A22,Retrieval!$B$2:$B$251,C22,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A22,Retrieval!$B$2:$B$305,C22,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -1401,29 +1402,29 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Extractor layout-ocr-v1</t>
+          <t>Recommended settings (v2)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="D23" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A23,Retrieval!$B$2:$B$251,C23,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A23,Retrieval!$B$2:$B$305,C23,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A23,Retrieval!$B$2:$B$251,C23,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A23,Retrieval!$B$2:$B$305,C23,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A23,Retrieval!$B$2:$B$251,C23,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A23,Retrieval!$B$2:$B$305,C23,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -1446,29 +1447,29 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1w</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Extractor layout-ocr-v1</t>
+          <t>Recommended, publish others with warnings</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D24" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A24,Retrieval!$B$2:$B$251,C24,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A24,Retrieval!$B$2:$B$305,C24,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A24,Retrieval!$B$2:$B$251,C24,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A24,Retrieval!$B$2:$B$305,C24,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A24,Retrieval!$B$2:$B$251,C24,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A24,Retrieval!$B$2:$B$305,C24,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -1491,29 +1492,29 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1w</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Extractor layout-ocr-v1</t>
+          <t>Recommended, publish others with warnings</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="D25" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A25,Retrieval!$B$2:$B$251,C25,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A25,Retrieval!$B$2:$B$305,C25,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A25,Retrieval!$B$2:$B$251,C25,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A25,Retrieval!$B$2:$B$305,C25,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A25,Retrieval!$B$2:$B$251,C25,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A25,Retrieval!$B$2:$B$305,C25,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -1536,29 +1537,29 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>R3a</t>
+          <t>R1w</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>OCR 300 DPI, 100 pages</t>
+          <t>Recommended, publish others with warnings</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="D26" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A26,Retrieval!$B$2:$B$251,C26,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A26,Retrieval!$B$2:$B$305,C26,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A26,Retrieval!$B$2:$B$251,C26,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A26,Retrieval!$B$2:$B$305,C26,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A26,Retrieval!$B$2:$B$251,C26,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A26,Retrieval!$B$2:$B$305,C26,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -1581,29 +1582,29 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>R3a</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>OCR 300 DPI, 100 pages</t>
+          <t>Extractor layout-ocr-v1</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D27" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A27,Retrieval!$B$2:$B$251,C27,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A27,Retrieval!$B$2:$B$305,C27,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A27,Retrieval!$B$2:$B$251,C27,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A27,Retrieval!$B$2:$B$305,C27,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A27,Retrieval!$B$2:$B$251,C27,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A27,Retrieval!$B$2:$B$305,C27,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -1626,29 +1627,29 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>R3a</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>OCR 300 DPI, 100 pages</t>
+          <t>Extractor layout-ocr-v1</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="D28" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A28,Retrieval!$B$2:$B$251,C28,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A28,Retrieval!$B$2:$B$305,C28,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A28,Retrieval!$B$2:$B$251,C28,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A28,Retrieval!$B$2:$B$305,C28,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A28,Retrieval!$B$2:$B$251,C28,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A28,Retrieval!$B$2:$B$305,C28,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -1671,29 +1672,29 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>R3b</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>OCR off</t>
+          <t>Extractor layout-ocr-v1</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="D29" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A29,Retrieval!$B$2:$B$251,C29,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A29,Retrieval!$B$2:$B$305,C29,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E29" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A29,Retrieval!$B$2:$B$251,C29,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A29,Retrieval!$B$2:$B$305,C29,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F29" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A29,Retrieval!$B$2:$B$251,C29,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A29,Retrieval!$B$2:$B$305,C29,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -1716,29 +1717,29 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>R3b</t>
+          <t>R3a</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>OCR off</t>
+          <t>OCR 300 DPI, 100 pages</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D30" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A30,Retrieval!$B$2:$B$251,C30,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A30,Retrieval!$B$2:$B$305,C30,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E30" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A30,Retrieval!$B$2:$B$251,C30,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A30,Retrieval!$B$2:$B$305,C30,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F30" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A30,Retrieval!$B$2:$B$251,C30,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A30,Retrieval!$B$2:$B$305,C30,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -1761,29 +1762,29 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>R3b</t>
+          <t>R3a</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>OCR off</t>
+          <t>OCR 300 DPI, 100 pages</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="D31" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A31,Retrieval!$B$2:$B$251,C31,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A31,Retrieval!$B$2:$B$305,C31,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E31" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A31,Retrieval!$B$2:$B$251,C31,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A31,Retrieval!$B$2:$B$305,C31,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F31" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A31,Retrieval!$B$2:$B$251,C31,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A31,Retrieval!$B$2:$B$305,C31,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G31" s="5">
@@ -1806,29 +1807,29 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3a</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Table evidence plain text</t>
+          <t>OCR 300 DPI, 100 pages</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="D32" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A32,Retrieval!$B$2:$B$251,C32,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A32,Retrieval!$B$2:$B$305,C32,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E32" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A32,Retrieval!$B$2:$B$251,C32,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A32,Retrieval!$B$2:$B$305,C32,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F32" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A32,Retrieval!$B$2:$B$251,C32,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A32,Retrieval!$B$2:$B$305,C32,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G32" s="5">
@@ -1851,29 +1852,29 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3b</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Table evidence plain text</t>
+          <t>OCR off</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D33" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A33,Retrieval!$B$2:$B$251,C33,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A33,Retrieval!$B$2:$B$305,C33,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E33" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A33,Retrieval!$B$2:$B$251,C33,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A33,Retrieval!$B$2:$B$305,C33,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F33" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A33,Retrieval!$B$2:$B$251,C33,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A33,Retrieval!$B$2:$B$305,C33,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G33" s="5">
@@ -1896,29 +1897,29 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3b</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Table evidence plain text</t>
+          <t>OCR off</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="D34" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A34,Retrieval!$B$2:$B$251,C34,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A34,Retrieval!$B$2:$B$305,C34,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E34" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A34,Retrieval!$B$2:$B$251,C34,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A34,Retrieval!$B$2:$B$305,C34,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F34" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A34,Retrieval!$B$2:$B$251,C34,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A34,Retrieval!$B$2:$B$305,C34,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G34" s="5">
@@ -1941,29 +1942,29 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R3b</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Chunks 300/400/40</t>
+          <t>OCR off</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="D35" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A35,Retrieval!$B$2:$B$251,C35,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A35,Retrieval!$B$2:$B$305,C35,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E35" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A35,Retrieval!$B$2:$B$251,C35,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A35,Retrieval!$B$2:$B$305,C35,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F35" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A35,Retrieval!$B$2:$B$251,C35,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A35,Retrieval!$B$2:$B$305,C35,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G35" s="5">
@@ -1986,29 +1987,29 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Chunks 300/400/40</t>
+          <t>Table evidence plain text</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D36" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A36,Retrieval!$B$2:$B$251,C36,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A36,Retrieval!$B$2:$B$305,C36,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E36" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A36,Retrieval!$B$2:$B$251,C36,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A36,Retrieval!$B$2:$B$305,C36,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F36" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A36,Retrieval!$B$2:$B$251,C36,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A36,Retrieval!$B$2:$B$305,C36,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G36" s="5">
@@ -2031,29 +2032,29 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Chunks 300/400/40</t>
+          <t>Table evidence plain text</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="D37" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A37,Retrieval!$B$2:$B$251,C37,Retrieval!$I$2:$I$251,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A37,Retrieval!$B$2:$B$305,C37,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E37" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A37,Retrieval!$B$2:$B$251,C37,Retrieval!$I$2:$I$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A37,Retrieval!$B$2:$B$305,C37,Retrieval!$I$2:$I$305,"yes")</f>
         <v/>
       </c>
       <c r="F37" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$251,A37,Retrieval!$B$2:$B$251,C37,Retrieval!$J$2:$J$251,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A37,Retrieval!$B$2:$B$305,C37,Retrieval!$J$2:$J$305,"yes")</f>
         <v/>
       </c>
       <c r="G37" s="5">
@@ -2074,126 +2075,322 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Table evidence plain text</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="D38" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A38,Retrieval!$B$2:$B$305,C38,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <v/>
+      </c>
+      <c r="E38" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A38,Retrieval!$B$2:$B$305,C38,Retrieval!$I$2:$I$305,"yes")</f>
+        <v/>
+      </c>
+      <c r="F38" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A38,Retrieval!$B$2:$B$305,C38,Retrieval!$J$2:$J$305,"yes")</f>
+        <v/>
+      </c>
+      <c r="G38" s="5">
+        <f>IF(D38=0,0,E38/D38)</f>
+        <v/>
+      </c>
+      <c r="H38" s="5">
+        <f>IF(D38=0,0,F38/D38)</f>
+        <v/>
+      </c>
+      <c r="I38" s="2">
+        <f>IF(COUNTIFS(Structure!$A:$A,A38,Structure!$C:$C,C38,Structure!$D:$D,"succeeded")&gt;0,"yes","no")</f>
+        <v/>
+      </c>
+      <c r="J38" s="2">
+        <f>IF(I38="no","Poor (not published)",IF(H38&gt;=0.9,"Good",IF(H38&gt;=0.75,"Acceptable","Poor")))</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Total embedding estimate (USD)</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr"/>
-      <c r="C39" s="2" t="inlineStr"/>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Chunks 300/400/40</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
       <c r="D39" s="2">
-        <f>Runs!S13</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A39,Retrieval!$B$2:$B$305,C39,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
+      <c r="E39" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A39,Retrieval!$B$2:$B$305,C39,Retrieval!$I$2:$I$305,"yes")</f>
+        <v/>
+      </c>
+      <c r="F39" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A39,Retrieval!$B$2:$B$305,C39,Retrieval!$J$2:$J$305,"yes")</f>
+        <v/>
+      </c>
+      <c r="G39" s="5">
+        <f>IF(D39=0,0,E39/D39)</f>
+        <v/>
+      </c>
+      <c r="H39" s="5">
+        <f>IF(D39=0,0,F39/D39)</f>
+        <v/>
+      </c>
+      <c r="I39" s="2">
+        <f>IF(COUNTIFS(Structure!$A:$A,A39,Structure!$C:$C,C39,Structure!$D:$D,"succeeded")&gt;0,"yes","no")</f>
+        <v/>
+      </c>
+      <c r="J39" s="2">
+        <f>IF(I39="no","Poor (not published)",IF(H39&gt;=0.9,"Good",IF(H39&gt;=0.75,"Acceptable","Poor")))</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Total answer cost (USD)</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="2" t="inlineStr"/>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Chunks 300/400/40</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
       <c r="D40" s="2">
-        <f>Answers!K31</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A40,Retrieval!$B$2:$B$305,C40,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
-      <c r="G40" s="2" t="n"/>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
+      <c r="E40" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A40,Retrieval!$B$2:$B$305,C40,Retrieval!$I$2:$I$305,"yes")</f>
+        <v/>
+      </c>
+      <c r="F40" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A40,Retrieval!$B$2:$B$305,C40,Retrieval!$J$2:$J$305,"yes")</f>
+        <v/>
+      </c>
+      <c r="G40" s="5">
+        <f>IF(D40=0,0,E40/D40)</f>
+        <v/>
+      </c>
+      <c r="H40" s="5">
+        <f>IF(D40=0,0,F40/D40)</f>
+        <v/>
+      </c>
+      <c r="I40" s="2">
+        <f>IF(COUNTIFS(Structure!$A:$A,A40,Structure!$C:$C,C40,Structure!$D:$D,"succeeded")&gt;0,"yes","no")</f>
+        <v/>
+      </c>
+      <c r="J40" s="2">
+        <f>IF(I40="no","Poor (not published)",IF(H40&gt;=0.9,"Good",IF(H40&gt;=0.75,"Acceptable","Poor")))</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Total spend (USD, embedding upper bound + recorded answers)</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr"/>
-      <c r="C41" s="2" t="inlineStr"/>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Chunks 300/400/40</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
       <c r="D41" s="2">
-        <f>D39+D40</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A41,Retrieval!$B$2:$B$305,C41,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
         <v/>
       </c>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
+      <c r="E41" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A41,Retrieval!$B$2:$B$305,C41,Retrieval!$I$2:$I$305,"yes")</f>
+        <v/>
+      </c>
+      <c r="F41" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A41,Retrieval!$B$2:$B$305,C41,Retrieval!$J$2:$J$305,"yes")</f>
+        <v/>
+      </c>
+      <c r="G41" s="5">
+        <f>IF(D41=0,0,E41/D41)</f>
+        <v/>
+      </c>
+      <c r="H41" s="5">
+        <f>IF(D41=0,0,F41/D41)</f>
+        <v/>
+      </c>
+      <c r="I41" s="2">
+        <f>IF(COUNTIFS(Structure!$A:$A,A41,Structure!$C:$C,C41,Structure!$D:$D,"succeeded")&gt;0,"yes","no")</f>
+        <v/>
+      </c>
+      <c r="J41" s="2">
+        <f>IF(I41="no","Poor (not published)",IF(H41&gt;=0.9,"Good",IF(H41&gt;=0.75,"Acceptable","Poor")))</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Spending cap (USD)</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr"/>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
-      <c r="G42" s="2" t="n"/>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="2" t="n"/>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>After fixes: recommended (v3)</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D42" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A42,Retrieval!$B$2:$B$305,C42,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <v/>
+      </c>
+      <c r="E42" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A42,Retrieval!$B$2:$B$305,C42,Retrieval!$I$2:$I$305,"yes")</f>
+        <v/>
+      </c>
+      <c r="F42" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A42,Retrieval!$B$2:$B$305,C42,Retrieval!$J$2:$J$305,"yes")</f>
+        <v/>
+      </c>
+      <c r="G42" s="5">
+        <f>IF(D42=0,0,E42/D42)</f>
+        <v/>
+      </c>
+      <c r="H42" s="5">
+        <f>IF(D42=0,0,F42/D42)</f>
+        <v/>
+      </c>
+      <c r="I42" s="2">
+        <f>IF(COUNTIFS(Structure!$A:$A,A42,Structure!$C:$C,C42,Structure!$D:$D,"succeeded")&gt;0,"yes","no")</f>
+        <v/>
+      </c>
+      <c r="J42" s="2">
+        <f>IF(I42="no","Poor (not published)",IF(H42&gt;=0.9,"Good",IF(H42&gt;=0.75,"Acceptable","Poor")))</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
-      <c r="J43" s="2" t="n"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>After fixes: recommended (v3)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D43" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A43,Retrieval!$B$2:$B$305,C43,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <v/>
+      </c>
+      <c r="E43" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A43,Retrieval!$B$2:$B$305,C43,Retrieval!$I$2:$I$305,"yes")</f>
+        <v/>
+      </c>
+      <c r="F43" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A43,Retrieval!$B$2:$B$305,C43,Retrieval!$J$2:$J$305,"yes")</f>
+        <v/>
+      </c>
+      <c r="G43" s="5">
+        <f>IF(D43=0,0,E43/D43)</f>
+        <v/>
+      </c>
+      <c r="H43" s="5">
+        <f>IF(D43=0,0,F43/D43)</f>
+        <v/>
+      </c>
+      <c r="I43" s="2">
+        <f>IF(COUNTIFS(Structure!$A:$A,A43,Structure!$C:$C,C43,Structure!$D:$D,"succeeded")&gt;0,"yes","no")</f>
+        <v/>
+      </c>
+      <c r="J43" s="2">
+        <f>IF(I43="no","Poor (not published)",IF(H43&gt;=0.9,"Good",IF(H43&gt;=0.75,"Acceptable","Poor")))</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Recommendation</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="n"/>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>After fixes: recommended (v3)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="D44" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A44,Retrieval!$B$2:$B$305,C44,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <v/>
+      </c>
+      <c r="E44" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A44,Retrieval!$B$2:$B$305,C44,Retrieval!$I$2:$I$305,"yes")</f>
+        <v/>
+      </c>
+      <c r="F44" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$305,A44,Retrieval!$B$2:$B$305,C44,Retrieval!$J$2:$J$305,"yes")</f>
+        <v/>
+      </c>
+      <c r="G44" s="5">
+        <f>IF(D44=0,0,E44/D44)</f>
+        <v/>
+      </c>
+      <c r="H44" s="5">
+        <f>IF(D44=0,0,F44/D44)</f>
+        <v/>
+      </c>
+      <c r="I44" s="2">
+        <f>IF(COUNTIFS(Structure!$A:$A,A44,Structure!$C:$C,C44,Structure!$D:$D,"succeeded")&gt;0,"yes","no")</f>
+        <v/>
+      </c>
+      <c r="J44" s="2">
+        <f>IF(I44="no","Poor (not published)",IF(H44&gt;=0.9,"Good",IF(H44&gt;=0.75,"Acceptable","Poor")))</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Keep visible: If a file can't be read well, Languages in scanned pages, Chunk size (target / maximum / overlap).</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="n"/>
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n"/>
@@ -2207,12 +2404,15 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Keep in Advanced: Extractor version (v1 / v2), Maximum OCR pages, Quality thresholds (empty pages, characters, OCR confidence, reading order, malformed tables), Language policy (allowlist, confidence, mixed languages).</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
+          <t>Total embedding estimate (USD)</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2">
+        <f>Runs!S15</f>
+        <v/>
+      </c>
       <c r="E46" s="2" t="n"/>
       <c r="F46" s="2" t="n"/>
       <c r="G46" s="2" t="n"/>
@@ -2223,12 +2423,15 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Candidate to remove: Read scanned pages (OCR), OCR resolution (DPI), Per-page OCR timeout, Detect rotation / deskew, Extraction strategy (Auto / Native / Layout-aware), Table evidence (Structured + Markdown / Markdown / Plain text).</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
+          <t>Total answer cost (USD)</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr"/>
+      <c r="D47" s="2">
+        <f>Answers!K51</f>
+        <v/>
+      </c>
       <c r="E47" s="2" t="n"/>
       <c r="F47" s="2" t="n"/>
       <c r="G47" s="2" t="n"/>
@@ -2239,18 +2442,131 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Fix first: X1 The recommended setting ('Stop and let me review') blocks an ordinary government report. | X2 Borderless PDF tables lose their rows: whole columns are merged into one cell, and cells over 1,000 characters are cut. | X3 'Publish the other files and show warnings' does not publish the others when a file cannot be read.</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n"/>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n"/>
+          <t>Total spend (USD, embedding upper bound + recorded answers)</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2">
+        <f>D46+D47</f>
+        <v/>
+      </c>
       <c r="E48" s="2" t="n"/>
       <c r="F48" s="2" t="n"/>
       <c r="G48" s="2" t="n"/>
       <c r="H48" s="2" t="n"/>
       <c r="I48" s="2" t="n"/>
       <c r="J48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Spending cap (USD)</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Keep visible: If a file can't be read well, Languages in scanned pages, Chunk size (target / maximum / overlap).</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Keep in Advanced: Extractor version (v1 / v2), Maximum OCR pages, Quality thresholds (empty pages, characters, OCR confidence, reading order, malformed tables), Language policy (allowlist, confidence, mixed languages).</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Candidate to remove: Read scanned pages (OCR), OCR resolution (DPI), Per-page OCR timeout, Detect rotation / deskew, Extraction strategy (Auto / Native / Layout-aware), Table evidence (Structured + Markdown / Markdown / Plain text).</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Fix first: X1 The recommended setting ('Stop and let me review') blocks an ordinary government report. | X2 Borderless PDF tables lose their rows: whole columns are merged into one cell, and cells over 1,000 characters are cut. | X3 'Publish the other files and show warnings' does not publish the others when a file cannot be read.</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2634,7 +2950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2656,6 +2972,8 @@
     <col width="8" customWidth="1" min="17" max="17"/>
     <col width="9" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2754,6 +3072,16 @@
           <t>Embedding cost est. (USD)</t>
         </is>
       </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Embedding tokens (app-reported)</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Embedding cost (app-reported, USD)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2833,6 +3161,16 @@
         <v>0</v>
       </c>
       <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2914,6 +3252,16 @@
       <c r="S3" s="2" t="n">
         <v>0.040144</v>
       </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2991,6 +3339,16 @@
       <c r="S4" s="2" t="n">
         <v>0.009011999999999999</v>
       </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3068,6 +3426,16 @@
       <c r="S5" s="2" t="n">
         <v>0.006846</v>
       </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3145,6 +3513,16 @@
       <c r="S6" s="2" t="n">
         <v>0.009011999999999999</v>
       </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3224,6 +3602,16 @@
         <v>0</v>
       </c>
       <c r="S7" s="2" t="n"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3301,6 +3689,16 @@
       <c r="S8" s="2" t="n">
         <v>0.008456</v>
       </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -3382,6 +3780,16 @@
       <c r="S9" s="2" t="n">
         <v>0.040144</v>
       </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3459,6 +3867,16 @@
       <c r="S10" s="2" t="n">
         <v>0.013111</v>
       </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3540,80 +3958,266 @@
       <c r="S11" s="2" t="n">
         <v>0.043422</v>
       </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
-      <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="2" t="n"/>
-      <c r="R12" s="2" t="n"/>
-      <c r="S12" s="2" t="n"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>After fixes: recommended (v3)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>layout-ocr-v3</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>preserve</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Stop and let me review</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>600 / 800 / 80</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>0.008666</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>After fixes: recommended (v3)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>n/a (HTML)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>n/a (HTML)</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Publish the other files and show warnings</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>600 / 800 / 80</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Reused R1 snapshot</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>2381</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>0.028906</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>137559</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>0.00275118</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="n"/>
+      <c r="T14" s="2" t="n"/>
+      <c r="U14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total embedding estimate (USD)</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr"/>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
-      <c r="L13" s="6" t="inlineStr"/>
-      <c r="M13" s="6" t="inlineStr"/>
-      <c r="N13" s="6" t="inlineStr"/>
-      <c r="O13" s="6" t="inlineStr"/>
-      <c r="P13" s="6" t="inlineStr"/>
-      <c r="Q13" s="6" t="inlineStr"/>
-      <c r="R13" s="6" t="inlineStr"/>
-      <c r="S13" s="6">
-        <f>SUM(S2:S11)</f>
+      <c r="B15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr"/>
+      <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr"/>
+      <c r="N15" s="6" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr"/>
+      <c r="P15" s="6" t="inlineStr"/>
+      <c r="Q15" s="6" t="inlineStr"/>
+      <c r="R15" s="6" t="inlineStr"/>
+      <c r="S15" s="6">
+        <f>SUM(S2:S13)</f>
         <v/>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Estimate basis: indexed UTF-8 bytes x $0.02 per million (OpenRouter list price for openai/text-embedding-3-small, 2026-10-09). Bytes overstate tokens, so this is an upper bound; the app does not record embedding cost.</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="7" t="n"/>
-      <c r="N14" s="7" t="n"/>
-      <c r="O14" s="7" t="n"/>
-      <c r="P14" s="7" t="n"/>
-      <c r="Q14" s="7" t="n"/>
-      <c r="R14" s="7" t="n"/>
-      <c r="S14" s="7" t="n"/>
+      <c r="T15" s="6" t="n"/>
+      <c r="U15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Estimate basis: indexed UTF-8 bytes x $0.02 per million (OpenRouter list price for openai/text-embedding-3-small, 2026-10-09). Bytes overstate tokens, so this is an upper bound. From A1 (spec 0007) the app records the provider-reported usage; earlier runs show 'not recorded'.</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="7" t="n"/>
+      <c r="N16" s="7" t="n"/>
+      <c r="O16" s="7" t="n"/>
+      <c r="P16" s="7" t="n"/>
+      <c r="Q16" s="7" t="n"/>
+      <c r="R16" s="7" t="n"/>
+      <c r="S16" s="7" t="n"/>
+      <c r="T16" s="7" t="n"/>
+      <c r="U16" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3626,7 +4230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5607,6 +6211,412 @@
         <v>32</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>575</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>795</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>640</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>543</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>465</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>616</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>1459</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>620</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>308.5</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>716</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>399</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>796</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5618,7 +6628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M251"/>
+  <dimension ref="A1:M305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -21705,6 +22715,3595 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>w1-q1</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>Which class does the Python tutorial recommend for implementing a queue?</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>collections.deque</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K252" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.python.org/3/tutorial/datastructures.html</t>
+        </is>
+      </c>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t>5. Data Structures ¶ &gt; 5.1. More on Lists ¶ &gt; 5.1.2. Using Lists as Queues ¶</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">e which was designed to
+have fast appends and pops from both ends.  For example:
+&gt;&gt;&gt; from collections import deque
+&gt;&gt;&gt; queue = deque(["Eric", "John", "Michael"])
+&gt;&gt;&gt; queue.append("Terry")           # Terry arrives
+&gt;&gt;&gt; queue.append("Graham")         </t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>w1-q2</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>In CPython 3.3, where is the compiled version of a module named spam.py cached?</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>spam.cpython-33.pyc</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K253" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.python.org/3/tutorial/modules.html</t>
+        </is>
+      </c>
+      <c r="L253" s="2" t="inlineStr">
+        <is>
+          <t>6. Modules ¶ &gt; 6.1. More on Modules ¶</t>
+        </is>
+      </c>
+      <c r="M253" s="2" t="inlineStr">
+        <is>
+          <t>6.1.3. “Compiled” Python files ¶
+To speed up loading modules, Python caches the compiled version of each module
+in the __pycache__ directory under the name module.version.pyc,
+where the version encodes the format of the compiled file; it generally c</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>w1-q3</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>What command does the tutorial use to create a virtual environment called tutorial-env?</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>python -m venv tutorial-env</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K254" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.python.org/3/tutorial/venv.html</t>
+        </is>
+      </c>
+      <c r="L254" s="2" t="inlineStr">
+        <is>
+          <t>12. Virtual Environments and Packages ¶</t>
+        </is>
+      </c>
+      <c r="M254" s="2" t="inlineStr">
+        <is>
+          <t>12.2. Creating Virtual Environments ¶
+The module used to create and manage virtual environments is called
+venv.  venv will install the Python version from which
+the command was run (as reported by the --version option).
+For instance, executing the c</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>w1-q4</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>When is the else clause of a for loop executed?</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>if no break occurred</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K255" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.python.org/3/tutorial/controlflow.html</t>
+        </is>
+      </c>
+      <c r="L255" s="2" t="inlineStr">
+        <is>
+          <t>4. More Control Flow Tools ¶ &gt; 4.5. else Clauses on Loops ¶</t>
+        </is>
+      </c>
+      <c r="M255" s="2" t="inlineStr">
+        <is>
+          <t>.  Look closely: the else clause belongs to
+the for loop, not the if statement.)
+One way to think of the else clause is to imagine it paired with the if
+inside the loop.  As the loop executes, it will run a sequence like
+if/if/if/else. The if is ins</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>w1-q5</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>What does the pass statement do?</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>the pass statement does nothing</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K256" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.python.org/3/tutorial/controlflow.html</t>
+        </is>
+      </c>
+      <c r="L256" s="2" t="inlineStr">
+        <is>
+          <t>4. More Control Flow Tools ¶</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="inlineStr">
+        <is>
+          <t>4.6. pass Statements ¶
+The pass statement does nothing. It can be used when a statement is
+required syntactically but the program requires no action. For example:
+&gt;&gt;&gt; while True:
+...     pass  # Busy-wait for keyboard interrupt (Ctrl+C)
+...
+This i</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>w1-q6</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>What does the list index() method return?</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>zero-based index of the first occurrence</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K257" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.mozilla.org/en-US/docs/Web/JavaScript/Reference/Global_Objects/Array</t>
+        </is>
+      </c>
+      <c r="L257" s="2" t="inlineStr">
+        <is>
+          <t>Array &gt; Description &gt; Iterative methods</t>
+        </is>
+      </c>
+      <c r="M257" s="2" t="inlineStr">
+        <is>
+          <t>Note the following:
+Not all methods do the i in this test. The find, findIndex, findLast, and findLastIndex methods do not, but other methods do.
+The length is memorized before the loop starts. This affects how insertions and deletions during itera</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>w1-q7</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>What is the short name for formatted string literals?</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>also called f-strings</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K258" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.python.org/3/tutorial/inputoutput.html</t>
+        </is>
+      </c>
+      <c r="L258" s="2" t="inlineStr">
+        <is>
+          <t>7. Input and Output ¶ &gt; 7.1. Fancier Output Formatting ¶ &gt; 7.1.1. Formatted String Literals ¶</t>
+        </is>
+      </c>
+      <c r="M258" s="2" t="inlineStr">
+        <is>
+          <t>a minimum
+number of characters wide.  This is useful for making columns line up.
+&gt;&gt;&gt; table = {'Sjoerd': 4127, 'Jack': 4098, 'Dcab': 7678}
+&gt;&gt;&gt; for name, phone in table.items():
+...     print(f'{name:10} ==&gt; {phone:10d}')
+...
+Sjoerd     ==&gt;       4127</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>w1-q8</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>On what date will Python 4.0 be released according to the tutorial?</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>unanswerable</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>(not in source)</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="n"/>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K259" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Python_(programming_language)</t>
+        </is>
+      </c>
+      <c r="L259" s="2" t="inlineStr">
+        <is>
+          <t>Python (programming language)</t>
+        </is>
+      </c>
+      <c r="M259" s="2" t="inlineStr">
+        <is>
+          <t>Guido van Rossum began working on Python in the late 1980s as a successor to the ABC programming language. Python 3.0, released in 2008, was a major revision and not completely backward-compatible with earlier versions. Beginning with Python 3.5, cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>w2-q1</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>What is the elevation of Mount Everest in metres?</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>8,848.86 m</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K260" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Mount_Everest</t>
+        </is>
+      </c>
+      <c r="L260" s="2" t="inlineStr">
+        <is>
+          <t>Mount Everest &gt; Surveys</t>
+        </is>
+      </c>
+      <c r="M260" s="2" t="inlineStr">
+        <is>
+          <t>21st century
+On 9 October 2005, after several months of measurement and calculation, the Chinese Academy of Sciences and State Bureau of Surveying and Mapping announced the height of Everest as 8,844.43 m (29,017.16 ft) with accuracy of ±0.21 m (8.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>w2-q2</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>How many individual reefs make up the Great Barrier Reef?</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>over 2,900 individual reefs</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K261" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Great_Barrier_Reef</t>
+        </is>
+      </c>
+      <c r="L261" s="2" t="inlineStr">
+        <is>
+          <t>Great Barrier Reef</t>
+        </is>
+      </c>
+      <c r="M261" s="2" t="inlineStr">
+        <is>
+          <t>The Great Barrier Reef is the world's largest coral reef system, composed of over 2,900 individual reefs and 900 islands stretching for over 2,300 kilometres (1,400 mi) over an area of approximately 344,400 square kilometres (133,000 mi2). The reef i</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>w2-q3</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>What is the average discharge of the Amazon River?</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>215,000 to 230,000 cubic meters per second</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K262" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Amazon_River</t>
+        </is>
+      </c>
+      <c r="L262" s="2" t="inlineStr">
+        <is>
+          <t>Amazon River</t>
+        </is>
+      </c>
+      <c r="M262" s="2" t="inlineStr">
+        <is>
+          <t>Discharge
+Average discharge at the estuary; Period from 2003 to 2015: 7,200 km3/a (230,000 m3/s)
+| Year | (km3) | (m3/s) | Year | (km3) | (m3/s) |
+| --- | --- | --- | --- | --- | --- |
+| 2003 | 6,470 | 205,000 | 2010 | 6,464 | 205,000 |
+| 2004 | 6,</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>w2-q4</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>When was the euro introduced to world financial markets as an accounting currency?</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>1 january 1999</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K263" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Euro</t>
+        </is>
+      </c>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> the highest combined values of banknotes and coins in circulation in the world.
+The name euro was officially adopted on 16 December 1995 in Madrid. The euro was introduced to world financial markets as an accounting currency on 1 January 1999, repl</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>w2-q5</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>Who published the first generally accepted periodic table, and in what year?</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>dmitri mendeleev in 1869</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K264" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Periodic_table</t>
+        </is>
+      </c>
+      <c r="L264" s="2" t="inlineStr">
+        <is>
+          <t>Periodic table</t>
+        </is>
+      </c>
+      <c r="M264" s="2" t="inlineStr">
+        <is>
+          <t>The first periodic table to become generally accepted was that of the Russian chemist Dmitri Mendeleev in 1869; he formulated the periodic law as a dependence of chemical properties on atomic mass. As not all elements were then known, there were gaps</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>w2-q6</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>What is the Moon's average distance from Earth?</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>378,000 kilometers</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K265" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Moon</t>
+        </is>
+      </c>
+      <c r="L265" s="2" t="inlineStr">
+        <is>
+          <t>Moon &gt; Earth–Moon system &gt; Orbit</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="inlineStr">
+        <is>
+          <t>arth, showing the Moon's far side when it is illuminated and the Moon's day-side
+The semi-major axis of the geocentric lunar orbit, called the lunar distance, is approximately 385,000 km (239,000 mi), or 1.3 light-seconds, comparable to going around</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>w2-q7</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>When was Python 3.0 released?</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>python 3.0, released in 2008</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K266" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Python_(programming_language)</t>
+        </is>
+      </c>
+      <c r="L266" s="2" t="inlineStr">
+        <is>
+          <t>Python (programming language)</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="inlineStr">
+        <is>
+          <t>Guido van Rossum began working on Python in the late 1980s as a successor to the ABC programming language. Python 3.0, released in 2008, was a major revision and not completely backward-compatible with earlier versions. Beginning with Python 3.5, cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>w2-q8</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>Who won the men's downhill at the 2030 Winter Olympics?</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>unanswerable</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>(not in source)</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="n"/>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K267" s="2" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Mount_Everest</t>
+        </is>
+      </c>
+      <c r="L267" s="2" t="inlineStr">
+        <is>
+          <t>Mount Everest</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="inlineStr">
+        <is>
+          <t>Extreme sports
+Mount Everest has been host to other winter sports and adventuring besides mountaineering, including snowboarding, skiing, paragliding, and BASE jumping.
+Yuichiro Miura became the first man to ski down Everest in the 1970s. He descen</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>w3-q1</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>What was the minimum hourly wage for workers under 18 from April 2024 to March 2025?</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>£6.40</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/national-minimum-wage-rates</t>
+        </is>
+      </c>
+      <c r="L268" s="2" t="inlineStr">
+        <is>
+          <t>National Minimum Wage and National Living Wage rates &gt; Previous rates</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rates between 1 April 2024 and 31 March 2026
+Since 1 April 2024 the National Living Wage has been for those aged 21 and over.
+|  | 21 and over | 18 to 20 | Under 18 | Apprentice |
+| --- | --- | --- | --- | --- |
+| April 2025 to March 2026 | £12.21 </t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>w3-q2</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>Which taxable income band does the 40% higher rate of Income Tax cover?</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>£50,271 to £125,140</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/income-tax-rates</t>
+        </is>
+      </c>
+      <c r="L269" s="2" t="inlineStr">
+        <is>
+          <t>Current rates and allowances</t>
+        </is>
+      </c>
+      <c r="M269" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Income Tax rates and bands
+The table shows the tax rates you pay in each band if you have a standard Personal Allowance of £12,570.
+Income tax bands are different if you live in Scotland.
+| Band | Taxable income | Tax rate |
+| --- | --- | --- |
+| </t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>w3-q3</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>How much Statutory Sick Pay can you get per week?</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>£123.25</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/statutory-sick-pay</t>
+        </is>
+      </c>
+      <c r="L270" s="2" t="inlineStr"/>
+      <c r="M270" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Overview
+You can get up to £123.25 per week Statutory Sick Pay (SSP) if you’re too ill to work. It’s paid by your employer for up to 28 weeks.
+This guide is also available in Welsh (Cymraeg).
+You cannot get less than the statutory amount. You can </t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>w3-q4</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>How many days of paid annual leave must a worker on a 5-day week receive?</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>at least 28 days</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/holiday-entitlement-rights</t>
+        </is>
+      </c>
+      <c r="L271" s="2" t="inlineStr">
+        <is>
+          <t>Entitlement</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="inlineStr">
+        <is>
+          <t>Statutory annual leave entitlement
+Most workers who work a 5-day week must receive at least 28 days’ paid annual leave a year. This is the equivalent of 5.6 weeks of holiday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>w3-q5</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>How long must you have worked for your employer to qualify for statutory redundancy pay?</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>at least 2 years</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/calculate-your-redundancy-pay</t>
+        </is>
+      </c>
+      <c r="L272" s="2" t="inlineStr"/>
+      <c r="M272" s="2" t="inlineStr">
+        <is>
+          <t>Calculate your statutory redundancy pay
+Calculate how much statutory redundancy you can get. It’s based on age, weekly pay and number of years in the job.
+Your weekly pay is the average you earned per week over the 12 weeks before the day you got y</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>w3-q6</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>What is the first vehicle tax payment for a petrol car emitting 111 to 130g/km of CO2?</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>111 to 130g/km + £455</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/vehicle-tax-rate-tables</t>
+        </is>
+      </c>
+      <c r="L273" s="2" t="inlineStr">
+        <is>
+          <t>Cars registered on or after 1 April 2017 &gt; First tax payment when you register the vehicle</t>
+        </is>
+      </c>
+      <c r="M273" s="2" t="inlineStr">
+        <is>
+          <t>ions. You can ask your car’s manufacturer if your car meets the RDE2 standard.
+| CO2 emissions | Diesel cars (TC49) that meet the RDE2 standard, petrol cars (TC48), Alternative fuel and zero emission cars | All other diesel cars (TC49) |
+| --- | ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>w3-q7</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>From when can an employee make a request for flexible working?</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>from their first day in a job</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/flexible-working</t>
+        </is>
+      </c>
+      <c r="L274" s="2" t="inlineStr"/>
+      <c r="M274" s="2" t="inlineStr">
+        <is>
+          <t>Overview
+Flexible working is a way of working that suits an employee’s needs, for example having flexible start and finish times, or working from home.
+Flexible working rules are different in Northern Ireland.
+All employees have the legal right to</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>w3-q8</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>What is the weekly rate of Statutory Paternity Pay?</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>unanswerable</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>(not in source)</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="n"/>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/statutory-sick-pay</t>
+        </is>
+      </c>
+      <c r="L275" s="2" t="inlineStr"/>
+      <c r="M275" s="2" t="inlineStr">
+        <is>
+          <t>Statutory Sick Pay (SSP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>w4-q1</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>What does HTTP status 418 I'm a teapot mean?</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>brew coffee with a teapot</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K276" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.mozilla.org/en-US/docs/Web/HTTP/Reference/Status</t>
+        </is>
+      </c>
+      <c r="L276" s="2" t="inlineStr">
+        <is>
+          <t>HTTP response status codes &gt; Client error responses</t>
+        </is>
+      </c>
+      <c r="M276" s="2" t="inlineStr">
+        <is>
+          <t>ted data is not supported by the server, so the server is rejecting the request.
+416 Range Not Satisfiable
+The ranges specified by the Range header field in the request cannot be fulfilled.
+It's possible that the range is outside the size of the ta</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>w4-q2</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>What does HTTP status 429 mean?</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>too many requests in a given amount of time</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K277" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.mozilla.org/en-US/docs/Web/HTTP/Reference/Status</t>
+        </is>
+      </c>
+      <c r="L277" s="2" t="inlineStr">
+        <is>
+          <t>HTTP response status codes &gt; Client error responses</t>
+        </is>
+      </c>
+      <c r="M277" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> sends an Upgrade header in a 426 response to indicate the required protocol(s).
+428 Precondition Required
+The origin server requires the request to be conditional.
+This response is intended to prevent the 'lost update' problem, where a client GETs</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>w4-q3</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>How must multiple Cache-Control directives be separated?</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>must be comma-separated</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K278" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.mozilla.org/en-US/docs/Web/HTTP/Reference/Headers/Cache-Control</t>
+        </is>
+      </c>
+      <c r="L278" s="2" t="inlineStr">
+        <is>
+          <t>Cache-Control header</t>
+        </is>
+      </c>
+      <c r="M278" s="2" t="inlineStr">
+        <is>
+          <t>Syntax
+Cache-Control: &lt;directive&gt;, &lt;directive&gt;, ...
+Cache directives follow these rules:
+Caching directives are case-insensitive. However, lowercase is recommended because some implementations do not recognize uppercase directives.
+Multiple direc</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>w4-q4</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>What is a closure in JavaScript?</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>combination of a function bundled together</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K279" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.mozilla.org/en-US/docs/Web/JavaScript/Guide/Closures</t>
+        </is>
+      </c>
+      <c r="L279" s="2" t="inlineStr"/>
+      <c r="M279" s="2" t="inlineStr">
+        <is>
+          <t>Closures
+A closure is the combination of a function bundled together (enclosed) with references to its surrounding state (the lexical environment). In other words, a closure gives a function access to its outer scope. In JavaScript, closures are cre</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>w4-q5</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>How many mandatory arguments does the fetch() method take?</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>one mandatory argument</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K280" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.mozilla.org/en-US/docs/Web/API/Fetch_API</t>
+        </is>
+      </c>
+      <c r="L280" s="2" t="inlineStr">
+        <is>
+          <t>Fetch API &gt; Specifications</t>
+        </is>
+      </c>
+      <c r="M280" s="2" t="inlineStr">
+        <is>
+          <t>| Specification |
+| --- |
+| Fetch # fetch-method |
+| Fetch # deferred-fetch |</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>w4-q6</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>What does the HTTP QUERY method do?</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>the query method initiates a server-side query</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K281" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.mozilla.org/en-US/docs/Web/HTTP/Reference/Methods</t>
+        </is>
+      </c>
+      <c r="L281" s="2" t="inlineStr"/>
+      <c r="M281" s="2" t="inlineStr">
+        <is>
+          <t>HTTP request methods
+HTTP defines a set of request methods to indicate the purpose of the request and what is expected if the request is successful.
+Although they can also be nouns, these request methods are sometimes referred to as HTTP verbs.
+Each</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>w4-q7</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>In MDN's CORS preflight example, what value is sent in the Access-Control-Max-Age header?</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>access-control-max-age: 86400</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="n"/>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K282" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.mozilla.org/en-US/docs/Web/HTTP/Guides/CORS</t>
+        </is>
+      </c>
+      <c r="L282" s="2" t="inlineStr">
+        <is>
+          <t>Cross-Origin Resource Sharing (CORS) &gt; The HTTP response headers</t>
+        </is>
+      </c>
+      <c r="M282" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Access-Control-Max-Age
+The Access-Control-Max-Age header indicates how long the results of a preflight request can be cached. For an example of a preflight request, see the above examples.
+Access-Control-Max-Age: &lt;delta-seconds&gt;
+The delta-seconds </t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>w4-q8</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>Which HTTP status code means Payment Accepted?</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>unanswerable</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>(not in source)</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="n"/>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J283" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K283" s="2" t="inlineStr">
+        <is>
+          <t>https://developer.mozilla.org/en-US/docs/Web/HTTP/Reference/Status</t>
+        </is>
+      </c>
+      <c r="L283" s="2" t="inlineStr">
+        <is>
+          <t>HTTP response status codes &gt; Successful responses</t>
+        </is>
+      </c>
+      <c r="M283" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">. This is typically the response sent after POST requests, or some PUT requests.
+202 Accepted
+The request has been received but not yet acted upon.
+It is noncommittal, since there is no way in HTTP to later send an asynchronous response indicating </t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>f1-q1</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>What are the layer, hidden size and attention head settings of BERT-base?</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>l=12, h=768, a=12</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J284" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K284" s="2" t="inlineStr">
+        <is>
+          <t>acl-n19-1423-bert.pdf</t>
+        </is>
+      </c>
+      <c r="L284" s="2" t="inlineStr">
+        <is>
+          <t>Language Understanding &gt; 5 Ablation Studies &gt; 5.3 Feature-based Approach with BERT</t>
+        </is>
+      </c>
+      <c r="M284" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.99 84.4 86.7 92.9 12 1024 16 3.54 85.7 86.9 93.3 24 1024 16 3.23 86.6 87.8 93.7
+Table 6:
+Ablation over BERT model size. #L = the
+number of layers; #H = hidden size; #A = number of attention heads. “LM (ppl)” is the masked LM perplexity
+of held-out </t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>f1-q2</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>What percentage of WordPiece tokens does BERT mask during pre-training?</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>15% of all wordpiece</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J285" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K285" s="2" t="inlineStr">
+        <is>
+          <t>acl-n19-1423-bert.pdf</t>
+        </is>
+      </c>
+      <c r="L285" s="2" t="inlineStr">
+        <is>
+          <t>Language Understanding &gt; 3 BERT &gt; 3.1 Pre-training BERT</t>
+        </is>
+      </c>
+      <c r="M285" s="2" t="inlineStr">
+        <is>
+          <t>), we only predict the masked words rather than reconstructing the entire input.
+Although this allows us to obtain a bidirectional pre-trained model, a downside is that we are creating a mismatch between pre-training and ﬁne-tuning, since the [MASK]</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>f1-q3</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>What GLUE score did BERT reach?</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>glue score to 80.5%</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J286" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K286" s="2" t="inlineStr">
+        <is>
+          <t>acl-n19-1423-bert.pdf</t>
+        </is>
+      </c>
+      <c r="L286" s="2" t="inlineStr">
+        <is>
+          <t>Language Understanding &gt; 4 Experiments &gt; 4.1 GLUE</t>
+        </is>
+      </c>
+      <c r="M286" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 85.8 88.9 66.4 79.6 BERTLARGE 86.7/85.9 72.1 92.7 94.9 60.5 86.5 89.3 70.1 82.1
+Table 1: GLUE Test results, scored by the evaluation server (https://gluebenchmark.com/leaderboard).
+The number below each task denotes the number of training examples.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>f1-q4</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>Which corpora were used to pre-train BERT?</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>bookscorpus (800m words)</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J287" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K287" s="2" t="inlineStr">
+        <is>
+          <t>acl-n19-1423-bert.pdf</t>
+        </is>
+      </c>
+      <c r="L287" s="2" t="inlineStr">
+        <is>
+          <t>Language Understanding &gt; 3 BERT &gt; 3.1 Pre-training BERT</t>
+        </is>
+      </c>
+      <c r="M287" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ks, where BERT transfers all parameters to initialize end-task model parameters.
+Pre-training data The pre-training procedure largely follows the existing literature on language model pre-training. For the pre-training corpus we use the BooksCorpus </t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>f1-q5</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>What SQuAD v1.1 Test F1 did BERT achieve?</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>93.2</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J288" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K288" s="2" t="inlineStr">
+        <is>
+          <t>acl-n19-1423-bert.pdf</t>
+        </is>
+      </c>
+      <c r="L288" s="2" t="inlineStr">
+        <is>
+          <t>Language Understanding &gt; 4 Experiments &gt; 4.2 SQuAD v1.1</t>
+        </is>
+      </c>
+      <c r="M288" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rst ﬁne-tuning on TriviaQA (Joshi
+et al., 2017) befor ﬁne-tuning on SQuAD.
+Our best performing system outperforms the top leaderboard system by +1.5 F1 in ensembling and +1.3 F1 as a single system. In fact, our single BERT model outperforms the top </t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>f1-q6</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>How many total parameters does BERT-large have?</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>total parameters=340m</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J289" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K289" s="2" t="inlineStr">
+        <is>
+          <t>acl-n19-1423-bert.pdf</t>
+        </is>
+      </c>
+      <c r="L289" s="2" t="inlineStr">
+        <is>
+          <t>Language Understanding &gt; 5 Ablation Studies &gt; 5.2 Effect of Model Size</t>
+        </is>
+      </c>
+      <c r="M289" s="2" t="inlineStr">
+        <is>
+          <t>e literature is (L=64, H=512, A=2) with 235M parameters (Al-Rfou et al., 2018). 
+By contrast, BERTBASE contains 110M parameters and BERTLARGE contains 340M parameters.
+It has long been known that increasing the model size will lead to continual imp</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>f1-q7</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>How many GPUs were used to train GPT-4?</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>unanswerable</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>(not in source)</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="n"/>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J290" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K290" s="2" t="inlineStr">
+        <is>
+          <t>acl-n19-1423-bert.pdf</t>
+        </is>
+      </c>
+      <c r="L290" s="2" t="inlineStr">
+        <is>
+          <t>Language Understanding &gt; 5 Ablation Studies &gt; 5.2 Effect of Model Size</t>
+        </is>
+      </c>
+      <c r="M290" s="2" t="inlineStr">
+        <is>
+          <t>Results on selected GLUE tasks are shown in Table 6. In this table, we report the average Dev Set accuracy from 5 random restarts of ﬁne-tuning. We can see that larger models lead to a strict accuracy improvement across all four datasets, even for MR</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>f2-q1</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>What was real median household income in the United States in 2022?</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>$74,580</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J291" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K291" s="2" t="inlineStr">
+        <is>
+          <t>census-p60-279.pdf</t>
+        </is>
+      </c>
+      <c r="L291" s="2" t="inlineStr">
+        <is>
+          <t>Income in the United States: 2022 &gt; HOUSEHOLD INCOME BY SELECTED CHARACTERISTICS &gt; All Households</t>
+        </is>
+      </c>
+      <c r="M291" s="2" t="inlineStr">
+        <is>
+          <t>All Households
+Real median household income 
+was $74,580 in 2022, 2.3 percent 
+lower than the 2021 estimate of 
+$76,330. It was 4.7 percent lower 
+than the 2019 median, the year 
+before the start of the COVID-19 
+pandemic and the corresponding 
+rece</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>f2-q2</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>By how much did real median household income change between 2021 and 2022?</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>2.3 percent</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J292" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K292" s="2" t="inlineStr">
+        <is>
+          <t>census-p60-279.pdf</t>
+        </is>
+      </c>
+      <c r="L292" s="2" t="inlineStr">
+        <is>
+          <t>Income in the United States: 2022 &gt; HOUSEHOLD INCOME BY SELECTED CHARACTERISTICS &gt; Change: 2021 to 2022
+2022 Median Income</t>
+        </is>
+      </c>
+      <c r="M292" s="2" t="inlineStr">
+        <is>
+          <t>Change: 2021 to 2022
+2022 Median Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>f2-q3</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>How did the money income Gini index change between 2021 and 2022?</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>from 0.494 to 0.488</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J293" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K293" s="2" t="inlineStr">
+        <is>
+          <t>census-p60-279.pdf</t>
+        </is>
+      </c>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t>Income in the United States: 2022 &gt; HOUSEHOLD INCOME BY SELECTED CHARACTERISTICS &gt; Money Income Inequality27</t>
+        </is>
+      </c>
+      <c r="M293" s="2" t="inlineStr">
+        <is>
+          <t>Money Income Inequality27
+The Gini index is a statistical mea sure of income inequality ranging 
+from 0.0 to 1.0. It measures the 
+amount that any two incomes 
+differ, on average, relative to 
+mean income. It is an indicator 
+of how far apart or “sp</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>f2-q4</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>What was the median income of married-couple households in 2022 according to Table A-1?</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>married-couple + 110,800</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J294" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K294" s="2" t="inlineStr">
+        <is>
+          <t>census-p60-279.pdf</t>
+        </is>
+      </c>
+      <c r="L294" s="2" t="inlineStr">
+        <is>
+          <t>Income in the United States: 2022 &gt; HOUSEHOLD INCOME BY SELECTED CHARACTERISTICS &gt; Type of Household8</t>
+        </is>
+      </c>
+      <c r="M294" s="2" t="inlineStr">
+        <is>
+          <t>Type of Household8
+The 2022 real median income of 
+family households declined by 
+2.9 percent from 2021, and the 
+real median income of marriedcouple families declined by 3.9 
+percent. Among family house holds, married couples had the 
+highest media</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>f2-q5</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>What was the median income of family households in 2022 according to Table A-1?</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>family households + 95,450</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J295" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K295" s="2" t="inlineStr">
+        <is>
+          <t>census-p60-279.pdf</t>
+        </is>
+      </c>
+      <c r="L295" s="2" t="inlineStr">
+        <is>
+          <t>Income in the United States: 2022 &gt; HOUSEHOLD INCOME BY SELECTED CHARACTERISTICS &gt; Type of Household8</t>
+        </is>
+      </c>
+      <c r="M295" s="2" t="inlineStr">
+        <is>
+          <t>Type of Household8
+The 2022 real median income of 
+family households declined by 
+2.9 percent from 2021, and the 
+real median income of marriedcouple families declined by 3.9 
+percent. Among family house holds, married couples had the 
+highest media</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>f2-q6</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>What was the median income of nonfamily households in 2022 according to Table A-1?</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>nonfamily households + 45,440</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J296" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K296" s="2" t="inlineStr">
+        <is>
+          <t>census-p60-279.pdf</t>
+        </is>
+      </c>
+      <c r="L296" s="2" t="inlineStr">
+        <is>
+          <t>Income in the United States: 2022 &gt; HOUSEHOLD INCOME BY SELECTED CHARACTERISTICS &gt; Type of Household8</t>
+        </is>
+      </c>
+      <c r="M296" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">an 
+income between these groups and 
+non-Hispanic White households 
+decreased.12
+Nonfamily households had a 
+median income of $45,440 in 
+2022, which was not significantly 
+different from 2021 (Figure 1 and 
+Table A-1). Nonfamily house holds with a </t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>f2-q7</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>What was the median household income in Canada in 2022?</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>unanswerable</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>(not in source)</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="n"/>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J297" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K297" s="2" t="inlineStr">
+        <is>
+          <t>census-p60-279.pdf</t>
+        </is>
+      </c>
+      <c r="L297" s="2" t="inlineStr">
+        <is>
+          <t>Income in the United States: 2022 &gt; HOUSEHOLD INCOME BY SELECTED CHARACTERISTICS &gt; All Households</t>
+        </is>
+      </c>
+      <c r="M297" s="2" t="inlineStr">
+        <is>
+          <t>All Households
+Real median household income 
+was $74,580 in 2022, 2.3 percent 
+lower than the 2021 estimate of 
+$76,330. It was 4.7 percent lower 
+than the 2019 median, the year 
+before the start of the COVID-19 
+pandemic and the corresponding 
+rece</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>f3-q1</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>How many television pictures does Part III of the Surveyor VI report present?</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>139 of the total number</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J298" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K298" s="2" t="inlineStr">
+        <is>
+          <t>surveyor-vi-tv-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L298" s="2" t="inlineStr"/>
+      <c r="M298" s="2" t="inlineStr">
+        <is>
+          <t>ists of selected pictures from Surveyor VI and appropriate explanatory material.
+This Part III presents 139 of the total number of television pictures transmitted to earth from the lunar surface, between November 10 and November 24, 1967; 46 mosaics</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>f3-q2</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>Between which dates were the Surveyor VI television pictures transmitted?</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>november 10 and november 24, 1967</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J299" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K299" s="2" t="inlineStr">
+        <is>
+          <t>surveyor-vi-tv-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L299" s="2" t="inlineStr"/>
+      <c r="M299" s="2" t="inlineStr">
+        <is>
+          <t>ists of selected pictures from Surveyor VI and appropriate explanatory material.
+This Part III presents 139 of the total number of television pictures transmitted to earth from the lunar surface, between November 10 and November 24, 1967; 46 mosaics</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>f3-q3</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>How many mosaics are included in Part III?</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>46 mosaics</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J300" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K300" s="2" t="inlineStr">
+        <is>
+          <t>surveyor-vi-tv-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L300" s="2" t="inlineStr"/>
+      <c r="M300" s="2" t="inlineStr">
+        <is>
+          <t>ists of selected pictures from Surveyor VI and appropriate explanatory material.
+This Part III presents 139 of the total number of television pictures transmitted to earth from the lunar surface, between November 10 and November 24, 1967; 46 mosaics</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>f3-q4</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>What is the mass of the Surveyor survey TV camera?</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>7.3-kg camera</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J301" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K301" s="2" t="inlineStr">
+        <is>
+          <t>surveyor-vi-tv-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L301" s="2" t="inlineStr"/>
+      <c r="M301" s="2" t="inlineStr">
+        <is>
+          <t>Il. Television Subsystem M. I. Smokler
+The Surveyor TV system is designed to obtain video pictures of the lunar surface, lunar sky, and portions of the landed spacecraft. It includes a survey camera capable of panoramic viewing, and a TV auxiliary t</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>f3-q5</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>Over what range can the Surveyor TV camera focus?</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>1.22 m to infinity</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J302" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K302" s="2" t="inlineStr">
+        <is>
+          <t>surveyor-vi-tv-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L302" s="2" t="inlineStr"/>
+      <c r="M302" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> was capable of providing either a
+Fig. II-5. Variable-focal-length lens assembly
+100-mm or 25-mm focal length, resulting in a vertical field of view of approximately 6.43 or 25.3 deg, respectively, as measured by the angular subtense of the vertic</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>f3-q6</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>What scene luminance range is the Surveyor camera designed to accommodate?</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>0.008 to 2600 ft-l</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J303" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K303" s="2" t="inlineStr">
+        <is>
+          <t>surveyor-vi-tv-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L303" s="2" t="inlineStr"/>
+      <c r="M303" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tification signals and to provide appropriate video mixing.
+A. Camera Description
+The slow-scan survey TV camera, shown in Figs. II-1 and II-2, provides images of the lunar surface over a 360-deg panorama. Each picture, or frame, is imaged through </t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>f3-q7</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>Which mission number in the Surveyor series was Surveyor VI?</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>the sixth in a series of unmanned lunar soft-landing missions</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J304" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K304" s="2" t="inlineStr">
+        <is>
+          <t>surveyor-vi-tv-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L304" s="2" t="inlineStr"/>
+      <c r="M304" s="2" t="inlineStr">
+        <is>
+          <t>Preface
+This three-part document constitutes the Project Mission Report on Surveyor VI, the sixth in a series of unmanned lunar soft-landing missions.
+Part I of this Technical Report consists of a technical description and an evaluation of engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>f3-q8</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>What was the landing site latitude of Surveyor VII?</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>unanswerable</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>(not in source)</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="n"/>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J305" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K305" s="2" t="inlineStr">
+        <is>
+          <t>surveyor-vi-tv-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L305" s="2" t="inlineStr"/>
+      <c r="M305" s="2" t="inlineStr">
+        <is>
+          <t>Preface
+This three-part document constitutes the Project Mission Report on Surveyor VI, the sixth in a series of unmanned lunar soft-landing missions.
+Part I of this Technical Report consists of a technical description and an evaluation of engineer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21716,7 +26315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -23330,54 +27929,1154 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>w1-q1</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Which class does the Python tutorial recommend for implementing a queue?</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>collections.deque</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>The Python tutorial recommends using `collections.deque` for implementing a queue because it is designed for fast appends and pops from both ends [S2, S1].</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.0005419</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>w1-q3</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>What command does the tutorial use to create a virtual environment called tutorial-env?</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>python -m venv tutorial-env</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>The tutorial uses the command `python -m venv tutorial-env` to create a virtual environment named tutorial-env [S1].</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0.0005854</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>w1-q8</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>On what date will Python 4.0 be released according to the tutorial?</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Not stated in the source.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_EVIDENCE. The provided text states that, according to Guido van Rossum, Python 4.0 will probably never exist [S2]. Therefore, there is no release date mentioned.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>correct-abstain</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Declined: the tutorial gives no date.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>No answer to support.</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0.000595</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>w2-q1</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>What is the elevation of Mount Everest in metres?</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>8,848.86 m (29,031.7 ft)</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>The new official height of Mount Everest, as jointly announced by China and Nepal on December 8, 2020, is 8,848.86 meters [S2].</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0.0006736999999999999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>w2-q3</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>What is the average discharge of the Amazon River?</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>About 215,000 to 230,000 cubic meters per second.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>The Amazon River has an average discharge of about 215,000 to 230,000 cubic meters per second [S2]. From 2003 to 2015, the average discharge at the estuary was 230,000 m3/s [S1].</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.001105</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>w2-q5</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Who published the first generally accepted periodic table, and in what year?</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Dmitri Mendeleev, in 1869.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>The first generally accepted periodic table was published by the Russian chemist Dmitri Mendeleev in 1869 [S1]. His printed table appeared in May 1869 in the journal of the Russian Chemical Society [S2].</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0.0005674</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>w3-q1</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>What was the minimum hourly wage for workers under 18 from April 2024 to March 2025?</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>£6.40</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>The minimum hourly wage for workers under 18 from April 2024 to March 2025 was £6.40 [S1].</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0.0006487</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>w3-q2</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Which taxable income band does the 40% higher rate of Income Tax cover?</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>£50,271 to £125,140</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>The 40% higher rate of Income Tax covers taxable income from £50,271 to £125,140 [S1].</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0.0004597</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>w3-q6</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>What is the first vehicle tax payment for a petrol car emitting 111 to 130g/km of CO2?</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>£455</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>The first vehicle tax payment for a petrol car emitting 111 to 130g/km of CO2 is £455 [S1]. This payment covers the vehicle for 12 months [S5].</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0.0007875</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>w4-q1</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>What does HTTP status 418 I'm a teapot mean?</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>The server refuses the attempt to brew coffee with a teapot.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>The HTTP status 418 I'm a teapot means that the server refuses to brew coffee with a teapot [S1].</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0.0005777999999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>w4-q4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>What is a closure in JavaScript?</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>The combination of a function bundled together with references to its surrounding state (the lexical environment).</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>A closure in JavaScript is the combination of a function and its surrounding state (the lexical environment) [S1]. It allows a function to access its outer scope [S1]. Closures are created every time a function is created [S1]. This means that a function maintains access to variables that were in scope when the closure was created, even after the outer function has finished executing [S3, S5].</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0.0006591</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>w4-q8</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Which HTTP status code means Payment Accepted?</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Not stated in the source (no such status code).</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_EVIDENCE. The provided documents do not list an HTTP status code that means "Payment Accepted." They do mention "402 Payment Required," but this is a different meaning [S2].</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>correct-abstain</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Declined: no such status code.</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>No answer to support.</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0.0005723</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>f1-q1</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>What are the layer, hidden size and attention head settings of BERT-base?</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>12 layers, hidden size 768, 12 attention heads (110M parameters).</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>BERT-base has 12 layers (L=12), a hidden size of 768 (H=768), and 12 attention heads (A=12) [S2].</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0.0007998</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>f1-q4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Which corpora were used to pre-train BERT?</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>BooksCorpus (800M words) and English Wikipedia (2,500M words).</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>The BooksCorpus (800M words) and English Wikipedia (2,500M words) were used to pre-train BERT [S1].</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0.0003391</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>f2-q1</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>What was real median household income in the United States in 2022?</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>$74,580</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Real median household income in the United States was $74,580 in 2022 [S1].</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.0006089</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>f2-q4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>What was the median income of married-couple households in 2022 according to Table A-1?</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>$110,800</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>The median income of married-couple households in 2022 was $110,800 [S1, S2].</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>States $110,800 from Table A-1 (was wrongly declined before the fixes).</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0.0008316</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>f2-q6</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>What was the median income of nonfamily households in 2022 according to Table A-1?</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>$45,440</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>The median income of nonfamily households in 2022 was $45,440 [S1, S4].</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.0007885</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>f3-q1</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>How many television pictures does Part III of the Surveyor VI report present?</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>139 pictures.</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Part III of the Surveyor VI report presents 139 television pictures [S1, S2].</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>0.0004443</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>f3-q4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>What is the mass of the Surveyor survey TV camera?</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>7.3 kg.</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>The Surveyor survey TV camera has a mass of 7.3 kg [S3].</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0.000513</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>f3-q8</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>What was the landing site latitude of Surveyor VII?</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Not stated in the source.</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_EVIDENCE. The provided documents discuss the Surveyor VI mission but do not contain information about the landing site latitude of Surveyor VII [S1, S2, S3, S4, S5].</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>correct-abstain</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Declined: the report covers Surveyor VI only.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>No answer to support.</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0.0004866</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
           <t>Total answer cost (USD)</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr"/>
-      <c r="C31" s="2" t="inlineStr"/>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2">
-        <f>SUM(K2:K29)</f>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2">
+        <f>SUM(K2:K49)</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Labels: correct, correct-abstain, partial, wrong, wrong-abstain. Scored blind by Claude with the spec 0004 rubric; rounds were hidden as X/Y.</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Labels: correct, correct-abstain, partial, wrong, wrong-abstain. Scored blind by Claude with the spec 0004 rubric; rounds were hidden as X/Y. A1 (after the fixes) was scored with the same rubric against the references, not blind.</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23931,7 +29630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -23940,6 +29639,8 @@
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23973,6 +29674,16 @@
           <t>Next step</t>
         </is>
       </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>After fixes (spec 0007)</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>After-fixes evidence</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -24005,6 +29716,16 @@
           <t>Fix X2; until then make malformed tables a warning in Balanced.</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>A1 files run with 'Stop and let me review' published all three files; the Census report is no longer blocked (layout-ocr-v3).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -24037,6 +29758,16 @@
           <t>New extractor version: detect merged-column tables (cells with many line-separated values) and fall back to text lines for those tables instead of truncating.</t>
         </is>
       </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>f2-q4 and f2-q5 now retrieve their Table A-1 row (rank 2 and 4; before: not in the top 5). f2-q4 answer changed from wrongly declined to correct ($110,800). Rotated landscape tables are kept whole but transposed (known limit).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -24069,6 +29800,16 @@
           <t>Either exclude any unreadable file under this choice, or reword it to match the behaviour.</t>
         </is>
       </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Fixed (tests)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Covered by PostgreSQL tests for files, S3 and Website runs: an unreadable item is skipped and the rest publish. Not re-run live: no A1 item failed.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -24101,6 +29842,16 @@
           <t>Render HTML tables as Markdown rows in the website extractor (new web extractor version).</t>
         </is>
       </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>A1 website index has 156 table chunks, all with a header row (R1: 0).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -24133,6 +29884,16 @@
           <t>Keep the hyphen when both parts are dictionary words or the hyphen is followed by a lowercase word that also appears hyphenated elsewhere.</t>
         </is>
       </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Mostly fixed</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4 of 5 'married-couple' occurrences in the Census report keep their hyphen; one still reads 'marriedcouple' (cause not yet traced).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -24165,6 +29926,16 @@
           <t>Consider excluding reference lists and footnotes from website chunks.</t>
         </is>
       </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>No chunk from a References/Notes/External links section and no 'Retrieved ...' citation text in the A1 website index.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -24197,6 +29968,16 @@
           <t>Show discovered-but-out-of-scope links as excluded with a reason, once each.</t>
         </is>
       </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Fixed (tests)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>PostgreSQL test: an out-of-scope link found twice is listed once as excluded/skipped. A1 reused the R1 snapshot, so no new crawl links were listed.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -24229,6 +30010,819 @@
           <t>Record provider-reported embedding tokens and cost per run.</t>
         </is>
       </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>The app recorded provider-reported embedding usage: websites 137,559 tokens / $0.0028; files 0 tokens / $0 (every vector reused).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>X9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>A combined citation such as [S1, S2] is recorded as invalid, so the answer shows no valid citation.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>A1: w1-q1, f2-q4, f2-q6, f3-q1 cite '[S1, S2]'-style groups and have valid=[]; R1 shows the same (w1-q1, w4-q4). validate_citations() treats the whole bracket as one label.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Correct, supported answers look uncited in the evidence view.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Split a bracket on commas before checking labels; add a test.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Found during the spec 0007 re-run; not part of spec 0007.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Before vs after the spec 0007 fixes (same website snapshot, files and questions)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Before: websites R1, files R1w (R1 files was blocked). After: A1 = extractor v3, files 'Stop and let me review', websites 'Publish the others'.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Track</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Measure</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hit@1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Hit@5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>25/28</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>27/28</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Recommended run published</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Embedding (app-reported)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>137559 tokens, $0.00275118</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Reused vectors add nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Hit@1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>9/19</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>9/19</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Hit@5</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>17/19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19/19</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Recommended run published</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>R1 files was blocked by the Census report</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Embedding (app-reported)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0 tokens, $0.0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Reused vectors add nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Answers correct or correctly declined</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>19/20</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>A1 scored against the references, not blind (one new round)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Questions whose retrieval changed</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Question text</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>First hit rank before</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>First hit rank after</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>w2-q2</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>How many individual reefs make up the Great Barrier Reef?</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>not in top 5</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>w2-q6</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>What is the Moon's average distance from Earth?</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>not in top 5</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>w2-q7</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>When was Python 3.0 released?</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>w3-q6</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>What is the first vehicle tax payment for a petrol car emitting 111 to 130g/km of CO2?</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>f2-q4</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>What was the median income of married-couple households in 2022 according to Table A-1?</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>not in top 5</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>f2-q5</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>What was the median income of family households in 2022 according to Table A-1?</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>not in top 5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Findings status</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Finding</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>After fixes</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>The recommended setting ('Stop and let me review') blocks an ordinary government report.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>A1 files run with 'Stop and let me review' published all three files; the Census report is no longer blocked (layout-ocr-v3).</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Borderless PDF tables lose their rows: whole columns are merged into one cell, and cells over 1,000 characters are cut.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>f2-q4 and f2-q5 now retrieve their Table A-1 row (rank 2 and 4; before: not in the top 5). f2-q4 answer changed from wrongly declined to correct ($110,800). Rotated landscape tables are kept whole but transposed (known limit).</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>X3</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>'Publish the other files and show warnings' does not publish the others when a file cannot be read.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Fixed (tests)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Covered by PostgreSQL tests for files, S3 and Website runs: an unreadable item is skipped and the rest publish. Not re-run live: no A1 item failed.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>X4</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Website tables are flattened to one value per line.</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>A1 website index has 156 table chunks, all with a header row (R1: 0).</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>X5</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Line-break de-hyphenation merges real hyphenated words.</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Mostly fixed</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>4 of 5 'married-couple' occurrences in the Census report keep their hyphen; one still reads 'marriedcouple' (cause not yet traced).</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>X6</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>On long Wikipedia articles the lead paragraph can rank below notes and references.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>No chunk from a References/Notes/External links section and no 'Retrieved ...' citation text in the A1 website index.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>X7</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Website run details list out-of-scope links as succeeded with 0 chunks, often twice.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Fixed (tests)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>PostgreSQL test: an out-of-scope link found twice is listed once as excluded/skipped. A1 reused the R1 snapshot, so no new crawl links were listed.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>X8</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Embedding cost is not recorded by the app.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>The app recorded provider-reported embedding usage: websites 137,559 tokens / $0.0028; files 0 tokens / $0 (every vector reused).</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>X9</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>A combined citation such as [S1, S2] is recorded as invalid, so the answer shows no valid citation.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Found during the spec 0007 re-run; not part of spec 0007.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>First A1 website run used html-main-v3, which dropped Python-docs links marked class reference and split sentences at citation markers. Re-run with html-main-v3.1. Its retrieval: hit@5 lost w1-q1, w1-q5, w2-q3, w2-q7 versus R1.</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/qa/real-source-2026-10/real-source-test.xlsx
+++ b/docs/qa/real-source-2026-10/real-source-test.xlsx
@@ -30054,12 +30054,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Found during the spec 0007 re-run; not part of spec 0007.</t>
+          <t>Found during the spec 0007 re-run. validate_citations() now splits [S1, S2] into S1 and S2, and the answer view links each valid source. Covered by tests; recorded A1 answers keep the citations stored at the time.</t>
         </is>
       </c>
     </row>
@@ -30792,12 +30792,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Found during the spec 0007 re-run; not part of spec 0007.</t>
+          <t>Found during the spec 0007 re-run. validate_citations() now splits [S1, S2] into S1 and S2, and the answer view links each valid source. Covered by tests; recorded A1 answers keep the citations stored at the time.</t>
         </is>
       </c>
       <c r="E34" s="2" t="n"/>

--- a/docs/qa/real-source-2026-10/real-source-test.xlsx
+++ b/docs/qa/real-source-2026-10/real-source-test.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings verdict" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="After fixes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Extract v4" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -496,7 +497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Real-source ingestion test (spec 0006), re-run after the spec 0007 fixes (A1)</t>
+          <t>Real-source ingestion test (spec 0006), re-run after the spec 0007 fixes (A1) and with extractor v4 (A2, spec 0008)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -606,15 +607,15 @@
         </is>
       </c>
       <c r="D5" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A5,Retrieval!$B$2:$B$305,C5,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A5,Retrieval!$B$2:$B$344,C5,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E5" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A5,Retrieval!$B$2:$B$305,C5,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A5,Retrieval!$B$2:$B$344,C5,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F5" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A5,Retrieval!$B$2:$B$305,C5,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A5,Retrieval!$B$2:$B$344,C5,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G5" s="5">
@@ -651,15 +652,15 @@
         </is>
       </c>
       <c r="D6" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A6,Retrieval!$B$2:$B$305,C6,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A6,Retrieval!$B$2:$B$344,C6,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E6" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A6,Retrieval!$B$2:$B$305,C6,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A6,Retrieval!$B$2:$B$344,C6,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A6,Retrieval!$B$2:$B$305,C6,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A6,Retrieval!$B$2:$B$344,C6,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -696,15 +697,15 @@
         </is>
       </c>
       <c r="D7" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A7,Retrieval!$B$2:$B$305,C7,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A7,Retrieval!$B$2:$B$344,C7,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E7" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A7,Retrieval!$B$2:$B$305,C7,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A7,Retrieval!$B$2:$B$344,C7,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F7" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A7,Retrieval!$B$2:$B$305,C7,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A7,Retrieval!$B$2:$B$344,C7,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -741,15 +742,15 @@
         </is>
       </c>
       <c r="D8" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A8,Retrieval!$B$2:$B$305,C8,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A8,Retrieval!$B$2:$B$344,C8,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E8" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A8,Retrieval!$B$2:$B$305,C8,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A8,Retrieval!$B$2:$B$344,C8,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F8" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A8,Retrieval!$B$2:$B$305,C8,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A8,Retrieval!$B$2:$B$344,C8,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G8" s="5">
@@ -786,15 +787,15 @@
         </is>
       </c>
       <c r="D9" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A9,Retrieval!$B$2:$B$305,C9,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A9,Retrieval!$B$2:$B$344,C9,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E9" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A9,Retrieval!$B$2:$B$305,C9,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A9,Retrieval!$B$2:$B$344,C9,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F9" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A9,Retrieval!$B$2:$B$305,C9,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A9,Retrieval!$B$2:$B$344,C9,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G9" s="5">
@@ -831,15 +832,15 @@
         </is>
       </c>
       <c r="D10" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A10,Retrieval!$B$2:$B$305,C10,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A10,Retrieval!$B$2:$B$344,C10,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E10" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A10,Retrieval!$B$2:$B$305,C10,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A10,Retrieval!$B$2:$B$344,C10,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F10" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A10,Retrieval!$B$2:$B$305,C10,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A10,Retrieval!$B$2:$B$344,C10,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G10" s="5">
@@ -876,15 +877,15 @@
         </is>
       </c>
       <c r="D11" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A11,Retrieval!$B$2:$B$305,C11,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A11,Retrieval!$B$2:$B$344,C11,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E11" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A11,Retrieval!$B$2:$B$305,C11,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A11,Retrieval!$B$2:$B$344,C11,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F11" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A11,Retrieval!$B$2:$B$305,C11,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A11,Retrieval!$B$2:$B$344,C11,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G11" s="5">
@@ -921,15 +922,15 @@
         </is>
       </c>
       <c r="D12" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A12,Retrieval!$B$2:$B$305,C12,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A12,Retrieval!$B$2:$B$344,C12,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E12" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A12,Retrieval!$B$2:$B$305,C12,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A12,Retrieval!$B$2:$B$344,C12,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F12" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A12,Retrieval!$B$2:$B$305,C12,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A12,Retrieval!$B$2:$B$344,C12,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -966,15 +967,15 @@
         </is>
       </c>
       <c r="D13" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A13,Retrieval!$B$2:$B$305,C13,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A13,Retrieval!$B$2:$B$344,C13,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E13" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A13,Retrieval!$B$2:$B$305,C13,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A13,Retrieval!$B$2:$B$344,C13,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F13" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A13,Retrieval!$B$2:$B$305,C13,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A13,Retrieval!$B$2:$B$344,C13,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -1011,15 +1012,15 @@
         </is>
       </c>
       <c r="D14" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A14,Retrieval!$B$2:$B$305,C14,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A14,Retrieval!$B$2:$B$344,C14,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E14" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A14,Retrieval!$B$2:$B$305,C14,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A14,Retrieval!$B$2:$B$344,C14,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F14" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A14,Retrieval!$B$2:$B$305,C14,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A14,Retrieval!$B$2:$B$344,C14,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -1056,15 +1057,15 @@
         </is>
       </c>
       <c r="D15" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A15,Retrieval!$B$2:$B$305,C15,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A15,Retrieval!$B$2:$B$344,C15,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E15" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A15,Retrieval!$B$2:$B$305,C15,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A15,Retrieval!$B$2:$B$344,C15,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F15" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A15,Retrieval!$B$2:$B$305,C15,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A15,Retrieval!$B$2:$B$344,C15,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -1101,15 +1102,15 @@
         </is>
       </c>
       <c r="D16" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A16,Retrieval!$B$2:$B$305,C16,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A16,Retrieval!$B$2:$B$344,C16,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E16" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A16,Retrieval!$B$2:$B$305,C16,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A16,Retrieval!$B$2:$B$344,C16,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F16" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A16,Retrieval!$B$2:$B$305,C16,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A16,Retrieval!$B$2:$B$344,C16,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -1146,15 +1147,15 @@
         </is>
       </c>
       <c r="D17" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A17,Retrieval!$B$2:$B$305,C17,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A17,Retrieval!$B$2:$B$344,C17,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E17" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A17,Retrieval!$B$2:$B$305,C17,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A17,Retrieval!$B$2:$B$344,C17,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F17" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A17,Retrieval!$B$2:$B$305,C17,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A17,Retrieval!$B$2:$B$344,C17,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -1191,15 +1192,15 @@
         </is>
       </c>
       <c r="D18" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A18,Retrieval!$B$2:$B$305,C18,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A18,Retrieval!$B$2:$B$344,C18,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E18" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A18,Retrieval!$B$2:$B$305,C18,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A18,Retrieval!$B$2:$B$344,C18,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F18" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A18,Retrieval!$B$2:$B$305,C18,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A18,Retrieval!$B$2:$B$344,C18,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -1236,15 +1237,15 @@
         </is>
       </c>
       <c r="D19" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A19,Retrieval!$B$2:$B$305,C19,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A19,Retrieval!$B$2:$B$344,C19,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E19" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A19,Retrieval!$B$2:$B$305,C19,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A19,Retrieval!$B$2:$B$344,C19,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F19" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A19,Retrieval!$B$2:$B$305,C19,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A19,Retrieval!$B$2:$B$344,C19,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -1281,15 +1282,15 @@
         </is>
       </c>
       <c r="D20" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A20,Retrieval!$B$2:$B$305,C20,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A20,Retrieval!$B$2:$B$344,C20,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E20" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A20,Retrieval!$B$2:$B$305,C20,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A20,Retrieval!$B$2:$B$344,C20,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F20" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A20,Retrieval!$B$2:$B$305,C20,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A20,Retrieval!$B$2:$B$344,C20,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -1326,15 +1327,15 @@
         </is>
       </c>
       <c r="D21" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A21,Retrieval!$B$2:$B$305,C21,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A21,Retrieval!$B$2:$B$344,C21,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E21" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A21,Retrieval!$B$2:$B$305,C21,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A21,Retrieval!$B$2:$B$344,C21,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F21" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A21,Retrieval!$B$2:$B$305,C21,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A21,Retrieval!$B$2:$B$344,C21,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -1371,15 +1372,15 @@
         </is>
       </c>
       <c r="D22" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A22,Retrieval!$B$2:$B$305,C22,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A22,Retrieval!$B$2:$B$344,C22,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E22" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A22,Retrieval!$B$2:$B$305,C22,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A22,Retrieval!$B$2:$B$344,C22,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F22" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A22,Retrieval!$B$2:$B$305,C22,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A22,Retrieval!$B$2:$B$344,C22,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -1416,15 +1417,15 @@
         </is>
       </c>
       <c r="D23" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A23,Retrieval!$B$2:$B$305,C23,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A23,Retrieval!$B$2:$B$344,C23,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E23" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A23,Retrieval!$B$2:$B$305,C23,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A23,Retrieval!$B$2:$B$344,C23,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F23" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A23,Retrieval!$B$2:$B$305,C23,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A23,Retrieval!$B$2:$B$344,C23,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -1461,15 +1462,15 @@
         </is>
       </c>
       <c r="D24" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A24,Retrieval!$B$2:$B$305,C24,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A24,Retrieval!$B$2:$B$344,C24,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E24" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A24,Retrieval!$B$2:$B$305,C24,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A24,Retrieval!$B$2:$B$344,C24,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F24" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A24,Retrieval!$B$2:$B$305,C24,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A24,Retrieval!$B$2:$B$344,C24,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -1506,15 +1507,15 @@
         </is>
       </c>
       <c r="D25" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A25,Retrieval!$B$2:$B$305,C25,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A25,Retrieval!$B$2:$B$344,C25,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E25" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A25,Retrieval!$B$2:$B$305,C25,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A25,Retrieval!$B$2:$B$344,C25,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F25" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A25,Retrieval!$B$2:$B$305,C25,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A25,Retrieval!$B$2:$B$344,C25,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -1551,15 +1552,15 @@
         </is>
       </c>
       <c r="D26" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A26,Retrieval!$B$2:$B$305,C26,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A26,Retrieval!$B$2:$B$344,C26,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E26" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A26,Retrieval!$B$2:$B$305,C26,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A26,Retrieval!$B$2:$B$344,C26,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F26" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A26,Retrieval!$B$2:$B$305,C26,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A26,Retrieval!$B$2:$B$344,C26,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -1596,15 +1597,15 @@
         </is>
       </c>
       <c r="D27" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A27,Retrieval!$B$2:$B$305,C27,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A27,Retrieval!$B$2:$B$344,C27,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E27" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A27,Retrieval!$B$2:$B$305,C27,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A27,Retrieval!$B$2:$B$344,C27,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F27" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A27,Retrieval!$B$2:$B$305,C27,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A27,Retrieval!$B$2:$B$344,C27,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -1641,15 +1642,15 @@
         </is>
       </c>
       <c r="D28" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A28,Retrieval!$B$2:$B$305,C28,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A28,Retrieval!$B$2:$B$344,C28,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E28" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A28,Retrieval!$B$2:$B$305,C28,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A28,Retrieval!$B$2:$B$344,C28,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F28" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A28,Retrieval!$B$2:$B$305,C28,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A28,Retrieval!$B$2:$B$344,C28,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -1686,15 +1687,15 @@
         </is>
       </c>
       <c r="D29" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A29,Retrieval!$B$2:$B$305,C29,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A29,Retrieval!$B$2:$B$344,C29,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E29" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A29,Retrieval!$B$2:$B$305,C29,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A29,Retrieval!$B$2:$B$344,C29,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F29" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A29,Retrieval!$B$2:$B$305,C29,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A29,Retrieval!$B$2:$B$344,C29,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -1731,15 +1732,15 @@
         </is>
       </c>
       <c r="D30" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A30,Retrieval!$B$2:$B$305,C30,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A30,Retrieval!$B$2:$B$344,C30,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E30" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A30,Retrieval!$B$2:$B$305,C30,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A30,Retrieval!$B$2:$B$344,C30,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F30" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A30,Retrieval!$B$2:$B$305,C30,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A30,Retrieval!$B$2:$B$344,C30,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -1776,15 +1777,15 @@
         </is>
       </c>
       <c r="D31" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A31,Retrieval!$B$2:$B$305,C31,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A31,Retrieval!$B$2:$B$344,C31,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E31" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A31,Retrieval!$B$2:$B$305,C31,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A31,Retrieval!$B$2:$B$344,C31,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F31" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A31,Retrieval!$B$2:$B$305,C31,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A31,Retrieval!$B$2:$B$344,C31,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G31" s="5">
@@ -1821,15 +1822,15 @@
         </is>
       </c>
       <c r="D32" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A32,Retrieval!$B$2:$B$305,C32,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A32,Retrieval!$B$2:$B$344,C32,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E32" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A32,Retrieval!$B$2:$B$305,C32,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A32,Retrieval!$B$2:$B$344,C32,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F32" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A32,Retrieval!$B$2:$B$305,C32,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A32,Retrieval!$B$2:$B$344,C32,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G32" s="5">
@@ -1866,15 +1867,15 @@
         </is>
       </c>
       <c r="D33" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A33,Retrieval!$B$2:$B$305,C33,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A33,Retrieval!$B$2:$B$344,C33,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E33" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A33,Retrieval!$B$2:$B$305,C33,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A33,Retrieval!$B$2:$B$344,C33,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F33" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A33,Retrieval!$B$2:$B$305,C33,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A33,Retrieval!$B$2:$B$344,C33,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G33" s="5">
@@ -1911,15 +1912,15 @@
         </is>
       </c>
       <c r="D34" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A34,Retrieval!$B$2:$B$305,C34,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A34,Retrieval!$B$2:$B$344,C34,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E34" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A34,Retrieval!$B$2:$B$305,C34,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A34,Retrieval!$B$2:$B$344,C34,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F34" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A34,Retrieval!$B$2:$B$305,C34,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A34,Retrieval!$B$2:$B$344,C34,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G34" s="5">
@@ -1956,15 +1957,15 @@
         </is>
       </c>
       <c r="D35" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A35,Retrieval!$B$2:$B$305,C35,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A35,Retrieval!$B$2:$B$344,C35,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E35" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A35,Retrieval!$B$2:$B$305,C35,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A35,Retrieval!$B$2:$B$344,C35,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F35" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A35,Retrieval!$B$2:$B$305,C35,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A35,Retrieval!$B$2:$B$344,C35,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G35" s="5">
@@ -2001,15 +2002,15 @@
         </is>
       </c>
       <c r="D36" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A36,Retrieval!$B$2:$B$305,C36,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A36,Retrieval!$B$2:$B$344,C36,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E36" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A36,Retrieval!$B$2:$B$305,C36,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A36,Retrieval!$B$2:$B$344,C36,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F36" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A36,Retrieval!$B$2:$B$305,C36,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A36,Retrieval!$B$2:$B$344,C36,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G36" s="5">
@@ -2046,15 +2047,15 @@
         </is>
       </c>
       <c r="D37" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A37,Retrieval!$B$2:$B$305,C37,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A37,Retrieval!$B$2:$B$344,C37,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E37" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A37,Retrieval!$B$2:$B$305,C37,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A37,Retrieval!$B$2:$B$344,C37,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F37" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A37,Retrieval!$B$2:$B$305,C37,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A37,Retrieval!$B$2:$B$344,C37,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G37" s="5">
@@ -2091,15 +2092,15 @@
         </is>
       </c>
       <c r="D38" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A38,Retrieval!$B$2:$B$305,C38,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A38,Retrieval!$B$2:$B$344,C38,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E38" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A38,Retrieval!$B$2:$B$305,C38,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A38,Retrieval!$B$2:$B$344,C38,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F38" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A38,Retrieval!$B$2:$B$305,C38,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A38,Retrieval!$B$2:$B$344,C38,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G38" s="5">
@@ -2136,15 +2137,15 @@
         </is>
       </c>
       <c r="D39" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A39,Retrieval!$B$2:$B$305,C39,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A39,Retrieval!$B$2:$B$344,C39,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E39" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A39,Retrieval!$B$2:$B$305,C39,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A39,Retrieval!$B$2:$B$344,C39,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F39" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A39,Retrieval!$B$2:$B$305,C39,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A39,Retrieval!$B$2:$B$344,C39,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G39" s="5">
@@ -2181,15 +2182,15 @@
         </is>
       </c>
       <c r="D40" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A40,Retrieval!$B$2:$B$305,C40,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A40,Retrieval!$B$2:$B$344,C40,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E40" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A40,Retrieval!$B$2:$B$305,C40,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A40,Retrieval!$B$2:$B$344,C40,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F40" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A40,Retrieval!$B$2:$B$305,C40,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A40,Retrieval!$B$2:$B$344,C40,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G40" s="5">
@@ -2226,15 +2227,15 @@
         </is>
       </c>
       <c r="D41" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A41,Retrieval!$B$2:$B$305,C41,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A41,Retrieval!$B$2:$B$344,C41,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E41" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A41,Retrieval!$B$2:$B$305,C41,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A41,Retrieval!$B$2:$B$344,C41,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F41" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A41,Retrieval!$B$2:$B$305,C41,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A41,Retrieval!$B$2:$B$344,C41,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G41" s="5">
@@ -2271,15 +2272,15 @@
         </is>
       </c>
       <c r="D42" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A42,Retrieval!$B$2:$B$305,C42,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A42,Retrieval!$B$2:$B$344,C42,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E42" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A42,Retrieval!$B$2:$B$305,C42,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A42,Retrieval!$B$2:$B$344,C42,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F42" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A42,Retrieval!$B$2:$B$305,C42,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A42,Retrieval!$B$2:$B$344,C42,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G42" s="5">
@@ -2316,15 +2317,15 @@
         </is>
       </c>
       <c r="D43" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A43,Retrieval!$B$2:$B$305,C43,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A43,Retrieval!$B$2:$B$344,C43,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E43" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A43,Retrieval!$B$2:$B$305,C43,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A43,Retrieval!$B$2:$B$344,C43,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F43" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A43,Retrieval!$B$2:$B$305,C43,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A43,Retrieval!$B$2:$B$344,C43,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G43" s="5">
@@ -2361,15 +2362,15 @@
         </is>
       </c>
       <c r="D44" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A44,Retrieval!$B$2:$B$305,C44,Retrieval!$I$2:$I$305,"&lt;&gt;n/a")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A44,Retrieval!$B$2:$B$344,C44,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
       <c r="E44" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A44,Retrieval!$B$2:$B$305,C44,Retrieval!$I$2:$I$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A44,Retrieval!$B$2:$B$344,C44,Retrieval!$I$2:$I$344,"yes")</f>
         <v/>
       </c>
       <c r="F44" s="2">
-        <f>COUNTIFS(Retrieval!$A$2:$A$305,A44,Retrieval!$B$2:$B$305,C44,Retrieval!$J$2:$J$305,"yes")</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A44,Retrieval!$B$2:$B$344,C44,Retrieval!$J$2:$J$344,"yes")</f>
         <v/>
       </c>
       <c r="G44" s="5">
@@ -2390,126 +2391,322 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n"/>
-      <c r="B45" s="2" t="n"/>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
-      <c r="G45" s="2" t="n"/>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="n"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Extract v4: recommended</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D45" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A45,Retrieval!$B$2:$B$344,C45,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
+        <v/>
+      </c>
+      <c r="E45" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A45,Retrieval!$B$2:$B$344,C45,Retrieval!$I$2:$I$344,"yes")</f>
+        <v/>
+      </c>
+      <c r="F45" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A45,Retrieval!$B$2:$B$344,C45,Retrieval!$J$2:$J$344,"yes")</f>
+        <v/>
+      </c>
+      <c r="G45" s="5">
+        <f>IF(D45=0,0,E45/D45)</f>
+        <v/>
+      </c>
+      <c r="H45" s="5">
+        <f>IF(D45=0,0,F45/D45)</f>
+        <v/>
+      </c>
+      <c r="I45" s="2">
+        <f>IF(COUNTIFS(Structure!$A:$A,A45,Structure!$C:$C,C45,Structure!$D:$D,"succeeded")&gt;0,"yes","no")</f>
+        <v/>
+      </c>
+      <c r="J45" s="2">
+        <f>IF(I45="no","Poor (not published)",IF(H45&gt;=0.9,"Good",IF(H45&gt;=0.75,"Acceptable","Poor")))</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Total embedding estimate (USD)</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr"/>
-      <c r="C46" s="2" t="inlineStr"/>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Extract v4: recommended</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
       <c r="D46" s="2">
-        <f>Runs!S15</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A46,Retrieval!$B$2:$B$344,C46,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
-      <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
+      <c r="E46" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A46,Retrieval!$B$2:$B$344,C46,Retrieval!$I$2:$I$344,"yes")</f>
+        <v/>
+      </c>
+      <c r="F46" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A46,Retrieval!$B$2:$B$344,C46,Retrieval!$J$2:$J$344,"yes")</f>
+        <v/>
+      </c>
+      <c r="G46" s="5">
+        <f>IF(D46=0,0,E46/D46)</f>
+        <v/>
+      </c>
+      <c r="H46" s="5">
+        <f>IF(D46=0,0,F46/D46)</f>
+        <v/>
+      </c>
+      <c r="I46" s="2">
+        <f>IF(COUNTIFS(Structure!$A:$A,A46,Structure!$C:$C,C46,Structure!$D:$D,"succeeded")&gt;0,"yes","no")</f>
+        <v/>
+      </c>
+      <c r="J46" s="2">
+        <f>IF(I46="no","Poor (not published)",IF(H46&gt;=0.9,"Good",IF(H46&gt;=0.75,"Acceptable","Poor")))</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Total answer cost (USD)</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr"/>
-      <c r="C47" s="2" t="inlineStr"/>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Extract v4: recommended</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
       <c r="D47" s="2">
-        <f>Answers!K51</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A47,Retrieval!$B$2:$B$344,C47,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
-      <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="2" t="n"/>
+      <c r="E47" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A47,Retrieval!$B$2:$B$344,C47,Retrieval!$I$2:$I$344,"yes")</f>
+        <v/>
+      </c>
+      <c r="F47" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A47,Retrieval!$B$2:$B$344,C47,Retrieval!$J$2:$J$344,"yes")</f>
+        <v/>
+      </c>
+      <c r="G47" s="5">
+        <f>IF(D47=0,0,E47/D47)</f>
+        <v/>
+      </c>
+      <c r="H47" s="5">
+        <f>IF(D47=0,0,F47/D47)</f>
+        <v/>
+      </c>
+      <c r="I47" s="2">
+        <f>IF(COUNTIFS(Structure!$A:$A,A47,Structure!$C:$C,C47,Structure!$D:$D,"succeeded")&gt;0,"yes","no")</f>
+        <v/>
+      </c>
+      <c r="J47" s="2">
+        <f>IF(I47="no","Poor (not published)",IF(H47&gt;=0.9,"Good",IF(H47&gt;=0.75,"Acceptable","Poor")))</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Total spend (USD, embedding upper bound + recorded answers)</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr"/>
-      <c r="C48" s="2" t="inlineStr"/>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Extract v4: recommended</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
       <c r="D48" s="2">
-        <f>D46+D47</f>
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A48,Retrieval!$B$2:$B$344,C48,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
         <v/>
       </c>
-      <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="n"/>
-      <c r="G48" s="2" t="n"/>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="2" t="n"/>
+      <c r="E48" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A48,Retrieval!$B$2:$B$344,C48,Retrieval!$I$2:$I$344,"yes")</f>
+        <v/>
+      </c>
+      <c r="F48" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A48,Retrieval!$B$2:$B$344,C48,Retrieval!$J$2:$J$344,"yes")</f>
+        <v/>
+      </c>
+      <c r="G48" s="5">
+        <f>IF(D48=0,0,E48/D48)</f>
+        <v/>
+      </c>
+      <c r="H48" s="5">
+        <f>IF(D48=0,0,F48/D48)</f>
+        <v/>
+      </c>
+      <c r="I48" s="2">
+        <f>IF(COUNTIFS(Structure!$A:$A,A48,Structure!$C:$C,C48,Structure!$D:$D,"succeeded")&gt;0,"yes","no")</f>
+        <v/>
+      </c>
+      <c r="J48" s="2">
+        <f>IF(I48="no","Poor (not published)",IF(H48&gt;=0.9,"Good",IF(H48&gt;=0.75,"Acceptable","Poor")))</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Spending cap (USD)</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr"/>
-      <c r="C49" s="2" t="inlineStr"/>
-      <c r="D49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="2" t="n"/>
-      <c r="F49" s="2" t="n"/>
-      <c r="G49" s="2" t="n"/>
-      <c r="H49" s="2" t="n"/>
-      <c r="I49" s="2" t="n"/>
-      <c r="J49" s="2" t="n"/>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Extract v4: recommended</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="D49" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A49,Retrieval!$B$2:$B$344,C49,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
+        <v/>
+      </c>
+      <c r="E49" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A49,Retrieval!$B$2:$B$344,C49,Retrieval!$I$2:$I$344,"yes")</f>
+        <v/>
+      </c>
+      <c r="F49" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A49,Retrieval!$B$2:$B$344,C49,Retrieval!$J$2:$J$344,"yes")</f>
+        <v/>
+      </c>
+      <c r="G49" s="5">
+        <f>IF(D49=0,0,E49/D49)</f>
+        <v/>
+      </c>
+      <c r="H49" s="5">
+        <f>IF(D49=0,0,F49/D49)</f>
+        <v/>
+      </c>
+      <c r="I49" s="2">
+        <f>IF(COUNTIFS(Structure!$A:$A,A49,Structure!$C:$C,C49,Structure!$D:$D,"succeeded")&gt;0,"yes","no")</f>
+        <v/>
+      </c>
+      <c r="J49" s="2">
+        <f>IF(I49="no","Poor (not published)",IF(H49&gt;=0.9,"Good",IF(H49&gt;=0.75,"Acceptable","Poor")))</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="n"/>
-      <c r="G50" s="2" t="n"/>
-      <c r="H50" s="2" t="n"/>
-      <c r="I50" s="2" t="n"/>
-      <c r="J50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Extract v4: recommended</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="D50" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A50,Retrieval!$B$2:$B$344,C50,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
+        <v/>
+      </c>
+      <c r="E50" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A50,Retrieval!$B$2:$B$344,C50,Retrieval!$I$2:$I$344,"yes")</f>
+        <v/>
+      </c>
+      <c r="F50" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A50,Retrieval!$B$2:$B$344,C50,Retrieval!$J$2:$J$344,"yes")</f>
+        <v/>
+      </c>
+      <c r="G50" s="5">
+        <f>IF(D50=0,0,E50/D50)</f>
+        <v/>
+      </c>
+      <c r="H50" s="5">
+        <f>IF(D50=0,0,F50/D50)</f>
+        <v/>
+      </c>
+      <c r="I50" s="2">
+        <f>IF(COUNTIFS(Structure!$A:$A,A50,Structure!$C:$C,C50,Structure!$D:$D,"succeeded")&gt;0,"yes","no")</f>
+        <v/>
+      </c>
+      <c r="J50" s="2">
+        <f>IF(I50="no","Poor (not published)",IF(H50&gt;=0.9,"Good",IF(H50&gt;=0.75,"Acceptable","Poor")))</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Recommendation</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n"/>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="n"/>
-      <c r="F51" s="2" t="n"/>
-      <c r="G51" s="2" t="n"/>
-      <c r="H51" s="2" t="n"/>
-      <c r="I51" s="2" t="n"/>
-      <c r="J51" s="2" t="n"/>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Extract v4: recommended</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="D51" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A51,Retrieval!$B$2:$B$344,C51,Retrieval!$I$2:$I$344,"&lt;&gt;n/a")</f>
+        <v/>
+      </c>
+      <c r="E51" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A51,Retrieval!$B$2:$B$344,C51,Retrieval!$I$2:$I$344,"yes")</f>
+        <v/>
+      </c>
+      <c r="F51" s="2">
+        <f>COUNTIFS(Retrieval!$A$2:$A$344,A51,Retrieval!$B$2:$B$344,C51,Retrieval!$J$2:$J$344,"yes")</f>
+        <v/>
+      </c>
+      <c r="G51" s="5">
+        <f>IF(D51=0,0,E51/D51)</f>
+        <v/>
+      </c>
+      <c r="H51" s="5">
+        <f>IF(D51=0,0,F51/D51)</f>
+        <v/>
+      </c>
+      <c r="I51" s="2">
+        <f>IF(COUNTIFS(Structure!$A:$A,A51,Structure!$C:$C,C51,Structure!$D:$D,"succeeded")&gt;0,"yes","no")</f>
+        <v/>
+      </c>
+      <c r="J51" s="2">
+        <f>IF(I51="no","Poor (not published)",IF(H51&gt;=0.9,"Good",IF(H51&gt;=0.75,"Acceptable","Poor")))</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Keep visible: If a file can't be read well, Languages in scanned pages, Chunk size (target / maximum / overlap).</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="n"/>
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n"/>
@@ -2523,12 +2720,15 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Keep in Advanced: Extractor version (v1 / v2), Maximum OCR pages, Quality thresholds (empty pages, characters, OCR confidence, reading order, malformed tables), Language policy (allowlist, confidence, mixed languages).</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n"/>
+          <t>Total embedding estimate (USD)</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2">
+        <f>Runs!S17</f>
+        <v/>
+      </c>
       <c r="E53" s="2" t="n"/>
       <c r="F53" s="2" t="n"/>
       <c r="G53" s="2" t="n"/>
@@ -2539,12 +2739,15 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Candidate to remove: Read scanned pages (OCR), OCR resolution (DPI), Per-page OCR timeout, Detect rotation / deskew, Extraction strategy (Auto / Native / Layout-aware), Table evidence (Structured + Markdown / Markdown / Plain text).</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
+          <t>Total answer cost (USD)</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2">
+        <f>Answers!K76</f>
+        <v/>
+      </c>
       <c r="E54" s="2" t="n"/>
       <c r="F54" s="2" t="n"/>
       <c r="G54" s="2" t="n"/>
@@ -2555,18 +2758,1239 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Fix first: X1 The recommended setting ('Stop and let me review') blocks an ordinary government report. | X2 Borderless PDF tables lose their rows: whole columns are merged into one cell, and cells over 1,000 characters are cut. | X3 'Publish the other files and show warnings' does not publish the others when a file cannot be read.</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
+          <t>Total spend (USD, embedding upper bound + recorded answers)</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2">
+        <f>D53+D54</f>
+        <v/>
+      </c>
       <c r="E55" s="2" t="n"/>
       <c r="F55" s="2" t="n"/>
       <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="n"/>
       <c r="J55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Spending cap (USD)</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
+      <c r="J57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Keep visible: If a file can't be read well, Languages in scanned pages, Chunk size (target / maximum / overlap).</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="n"/>
+      <c r="J59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Keep in Advanced: Extractor version (v1 / v2), Maximum OCR pages, Quality thresholds (empty pages, characters, OCR confidence, reading order, malformed tables), Language policy (allowlist, confidence, mixed languages).</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="n"/>
+      <c r="J60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Candidate to remove: Read scanned pages (OCR), OCR resolution (DPI), Per-page OCR timeout, Detect rotation / deskew, Extraction strategy (Auto / Native / Layout-aware), Table evidence (Structured + Markdown / Markdown / Plain text).</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="2" t="n"/>
+      <c r="I61" s="2" t="n"/>
+      <c r="J61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Fix first: X1 The recommended setting ('Stop and let me review') blocks an ordinary government report. | X2 Borderless PDF tables lose their rows: whole columns are merged into one cell, and cells over 1,000 characters are cut. | X3 'Publish the other files and show warnings' does not publish the others when a file cannot be read.</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="n"/>
+      <c r="F62" s="2" t="n"/>
+      <c r="G62" s="2" t="n"/>
+      <c r="H62" s="2" t="n"/>
+      <c r="I62" s="2" t="n"/>
+      <c r="J62" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Extractor v4 against v3 on real files (spec 0008, round A2)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Before: A1 = extractor v3, Maximum OCR pages 50. After: A2 = extractor v4, Maximum OCR pages 100, other Extract settings at the recommended values. The spec 0006 files use 'Stop and let me review'; the new files (F4-F7) use 'Publish the other files and show warnings'. Websites reuse the A1 index: v4 does not change the website reader.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Measure</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>A1 (v3)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>A2 (v4)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hit@1, spec 0006 file questions</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>9/19</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>10/19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Hit@5, spec 0006 file questions</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>19/19</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>19/19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>File questions found in A1 and missed in A2</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>files run</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>637 chunks; embedding 57835 tokens, $0.0011567 (app-reported)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>new run</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1030 chunks; embedding 94681 tokens, $0.00189362 (app-reported)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Answers correct or correctly declined, spec 0006 file questions</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>8/8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>File answers correct in A1 and not in A2</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Answers correct or correctly declined, new questions</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>11/17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>New questions (written from the source files)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Question text</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Reference answer</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>First hit rank (A2)</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Answer label (A2)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>f2-q9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>According to Table A-2, what was the median household income for all races in 2015, in 2022 dollars?</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>$68,410</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>not in top 5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>wrong-abstain</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Declined; the Table A-2 2015 row is in the index (correct, read row by row) but not in the top 5, which held the 2019-2022 rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>f2-q10</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>According to Table A-2, what was the mean household income for all races in 1990, in 2022 dollars?</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>$76,820</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>not in top 5</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>wrong-abstain</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Declined; the 1990 row is in the index but not in the top 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>f4-q1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Combien de décès dus aux maladies de l'appareil circulatoire pour 100 000 habitants l'UE-28 comptait-elle en 2015 ?</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>381 décès pour 100 000 habitants</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>not in top 5</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>wrong-abstain</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Declined; the chart callout '381 deces' is not in the index (chart read as an empty table).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>f4-q2</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>En 2015, combien de fois plus de risques de mourir d'une maladie de l'appareil circulatoire avait une personne vivant en Bulgarie qu'une personne vivant en France ?</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5,5 fois plus</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5,5 fois, as the reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>f4-q3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Quelle part des marchandises transportées dans l'UE-28 l'est par la route ?</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>77 %</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>77 %, as the reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>f4-q4</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>De combien les émissions de gaz à effet de serre de l'UE-28 ont-elles baissé par rapport à 1990 ?</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>De 22 % par rapport à 1990</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>not in top 5</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>22,4 % against 1990 (the prose figure; the chart callout rounds it to 22 %).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>f5-q1</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Who prepared the compilation of the 1950 water-use estimates in USGS Circular 115?</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Kenneth A. MacKichan</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>f5-q2</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>According to Table 1 of USGS Circular 115, how much surface water did municipalities in Illinois use in 1950 (mgd)?</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1,070 mgd</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>not in top 5</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>wrong-abstain</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Declined; the OCR row 'Illinois ... 1,070' is in the index but not in the top 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>f5-q3</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>According to Table 1 of USGS Circular 115, how much ground water did municipalities in Kansas use in 1950 (mgd)?</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>75 mgd</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>wrong-abstain</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Declined; the Kansas row is not in the top 5, and OCR reads its 75 as 78.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>f6-q1</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>What is the word limit for section A3.2, on tackling potholes, in the DfT highways maintenance transparency report template?</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>250 words</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>not in top 5</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>wrong-abstain</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Declined; the rank-1 chunk has 'Word limit - 250 words' but the A3.2 heading is in an earlier chunk, so the model could not tie the limit to A3.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>f6-q2</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Into which asset categories does table A4.1 of the DfT template break down spending on highways maintenance?</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Carriageways, footways, structures, drainage, street lighting and other assets</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>All six categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>f7-q1</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>In the Prevent risk assessment example matrix, what score range counts as medium risk?</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>7 to 11</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>7 to 11, from the slide table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>f7-q2</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>In the Prevent risk assessment matrix, which severity of impact has the same rating as a 'Very likely' probability?</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Major (rating 4)</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Major, rating 4, from the slide table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>f7-q3</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>According to the Prevent slides, on what scale are the severity and likelihood of risks usually ranked?</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>A 1-5 scale</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>1-5 scale, from the slide table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>f7-q4</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>unanswerable</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>What score marks a critical risk in the Prevent risk assessment matrix?</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Not stated in the source (the highest band is High risk, 12+).</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>correct-abstain</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Declined; the matrix has no critical band.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>f5-q4</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>unanswerable</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>How much water did Alaska withdraw for irrigation in 1950 according to USGS Circular 115?</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Not stated in the source.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>correct-abstain</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Declined; Alaska is not in Table 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>f4-q5</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>unanswerable</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Quel était le taux de chômage au Japon en 2018 selon ce rapport ?</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Not stated in the source.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>correct-abstain</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Declined; not in the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Questions whose retrieval changed from A1 to A2</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Question text</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>First hit rank A1</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>First hit rank A2</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>f2-q4</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>What was the median income of married-couple households in 2022 according to Table A-1?</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2579,7 +4003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2939,6 +4363,170 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>File (PDF)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Eurostat, Chiffres clés sur l'Europe, édition 2019 (French)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/documents/3217494/10164473/KS-EI-19-001-FR_N.pdf/aef66e0b-f5fe-c4e1-67ac-3c3f01a44384</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>© European Union, 2019; reuse authorised with attribution (Commission Decision 2011/833/EU)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>76 pages</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>9457b14c2fb44527eeb718ba7753bc5781d771db2b88447a723a42c65b5776af</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>File (PDF)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>USGS Circular 115, Estimated use of water in the United States, 1950 (1951 scan), image-only copy</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>https://pubs.usgs.gov/circ/1951/0115/report.pdf</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Public domain (US federal government work)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16 pages</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7c1d9fe14a6c7d7d065bfc3d018ef32fefc692ce36524dace01fd0908a181c23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>File (DOCX)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>DfT, Local highways maintenance transparency report template (DOCX)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/6a26d314f56856fd11c0b191/highways-maintenance-reports-template.docx</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Open Government Licence v3.0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>eb468aeba7ed8ff0bac3382ddeaa8e56dc859bc9dc3d988d4389a1fe508dfc02</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>File (PPTX)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Home Office/DfE, Designing and building a Prevent risk assessment (PPTX, 14 slides, 3 tables)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>https://assets.publishing.service.gov.uk/media/60a3d4a7d3bf7f28855b8ffd/Designing_and_building_a_Prevent_risk_assessment.pptx</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Open Government Licence v3.0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>14 pages</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>71e2e0fe0eacbb94867329cae876e1f119e8d2e7f76145cf289d12cb7873484f</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2950,7 +4538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4140,84 +5728,250 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n"/>
-      <c r="R14" s="2" t="n"/>
-      <c r="S14" s="2" t="n"/>
-      <c r="T14" s="2" t="n"/>
-      <c r="U14" s="2" t="n"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Extract v4: recommended</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>layout-ocr-v4</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>preserve</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Stop and let me review</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>600 / 800 / 80</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>637</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>0.007748</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>57835</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>0.0011567</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Extract v4: recommended</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>layout-ocr-v4</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>preserve</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Publish the other files and show warnings</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>600 / 800 / 80</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>1030</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>0.005961</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>94681</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>0.00189362</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="n"/>
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n"/>
+      <c r="T16" s="2" t="n"/>
+      <c r="U16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Total embedding estimate (USD)</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr"/>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
-      <c r="L15" s="6" t="inlineStr"/>
-      <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="6" t="inlineStr"/>
-      <c r="O15" s="6" t="inlineStr"/>
-      <c r="P15" s="6" t="inlineStr"/>
-      <c r="Q15" s="6" t="inlineStr"/>
-      <c r="R15" s="6" t="inlineStr"/>
-      <c r="S15" s="6">
-        <f>SUM(S2:S13)</f>
+      <c r="B17" s="6" t="inlineStr"/>
+      <c r="C17" s="6" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr"/>
+      <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr"/>
+      <c r="N17" s="6" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr"/>
+      <c r="P17" s="6" t="inlineStr"/>
+      <c r="Q17" s="6" t="inlineStr"/>
+      <c r="R17" s="6" t="inlineStr"/>
+      <c r="S17" s="6">
+        <f>SUM(S2:S15)</f>
         <v/>
       </c>
-      <c r="T15" s="6" t="n"/>
-      <c r="U15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="T17" s="6" t="n"/>
+      <c r="U17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Estimate basis: indexed UTF-8 bytes x $0.02 per million (OpenRouter list price for openai/text-embedding-3-small, 2026-10-09). Bytes overstate tokens, so this is an upper bound. From A1 (spec 0007) the app records the provider-reported usage; earlier runs show 'not recorded'.</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
-      <c r="N16" s="7" t="n"/>
-      <c r="O16" s="7" t="n"/>
-      <c r="P16" s="7" t="n"/>
-      <c r="Q16" s="7" t="n"/>
-      <c r="R16" s="7" t="n"/>
-      <c r="S16" s="7" t="n"/>
-      <c r="T16" s="7" t="n"/>
-      <c r="U16" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="7" t="n"/>
+      <c r="L18" s="7" t="n"/>
+      <c r="M18" s="7" t="n"/>
+      <c r="N18" s="7" t="n"/>
+      <c r="O18" s="7" t="n"/>
+      <c r="P18" s="7" t="n"/>
+      <c r="Q18" s="7" t="n"/>
+      <c r="R18" s="7" t="n"/>
+      <c r="S18" s="7" t="n"/>
+      <c r="T18" s="7" t="n"/>
+      <c r="U18" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4230,7 +5984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6617,6 +8371,412 @@
         <v>18</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>575</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>795</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>455</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>631</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>files</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>543</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>899</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>649</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>628</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>780</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>succeeded</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>378</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>785</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6628,7 +8788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M305"/>
+  <dimension ref="A1:M344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -26304,6 +28464,2599 @@
         </is>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>f1-q1</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>What are the layer, hidden size and attention head settings of BERT-base?</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>l=12, h=768, a=12</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J306" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K306" s="2" t="inlineStr">
+        <is>
+          <t>acl-n19-1423-bert.pdf</t>
+        </is>
+      </c>
+      <c r="L306" s="2" t="inlineStr">
+        <is>
+          <t>Language Understanding &gt; 5 Ablation Studies &gt; 5.3 Feature-based Approach with BERT</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">.99 84.4 86.7 92.9 12 1024 16 3.54 85.7 86.9 93.3 24 1024 16 3.23 86.6 87.8 93.7
+Table 6:
+Ablation over BERT model size. #L = the
+number of layers; #H = hidden size; #A = number of attention heads. “LM (ppl)” is the masked LM perplexity
+of held-out </t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>f1-q2</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>What percentage of WordPiece tokens does BERT mask during pre-training?</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>15% of all wordpiece</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K307" s="2" t="inlineStr">
+        <is>
+          <t>acl-n19-1423-bert.pdf</t>
+        </is>
+      </c>
+      <c r="L307" s="2" t="inlineStr">
+        <is>
+          <t>Language Understanding &gt; 3 BERT &gt; 3.1 Pre-training BERT</t>
+        </is>
+      </c>
+      <c r="M307" s="2" t="inlineStr">
+        <is>
+          <t>), we only predict the masked words rather than reconstructing the entire input.
+Although this allows us to obtain a bidirectional pre-trained model, a downside is that we are creating a mismatch between pre-training and ﬁne-tuning, since the [MASK]</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>f1-q3</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>What GLUE score did BERT reach?</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>glue score to 80.5%</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K308" s="2" t="inlineStr">
+        <is>
+          <t>acl-n19-1423-bert.pdf</t>
+        </is>
+      </c>
+      <c r="L308" s="2" t="inlineStr">
+        <is>
+          <t>Language Understanding &gt; 4 Experiments &gt; 4.1 GLUE</t>
+        </is>
+      </c>
+      <c r="M308" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 85.8 88.9 66.4 79.6 BERTLARGE 86.7/85.9 72.1 92.7 94.9 60.5 86.5 89.3 70.1 82.1
+Table 1: GLUE Test results, scored by the evaluation server (https://gluebenchmark.com/leaderboard).
+The number below each task denotes the number of training examples.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>f1-q4</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>Which corpora were used to pre-train BERT?</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>bookscorpus (800m words)</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J309" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K309" s="2" t="inlineStr">
+        <is>
+          <t>acl-n19-1423-bert.pdf</t>
+        </is>
+      </c>
+      <c r="L309" s="2" t="inlineStr">
+        <is>
+          <t>Language Understanding &gt; 3 BERT &gt; 3.1 Pre-training BERT</t>
+        </is>
+      </c>
+      <c r="M309" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ks, where BERT transfers all parameters to initialize end-task model parameters.
+Pre-training data The pre-training procedure largely follows the existing literature on language model pre-training. For the pre-training corpus we use the BooksCorpus </t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>f1-q5</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>What SQuAD v1.1 Test F1 did BERT achieve?</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>93.2</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J310" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K310" s="2" t="inlineStr">
+        <is>
+          <t>acl-n19-1423-bert.pdf</t>
+        </is>
+      </c>
+      <c r="L310" s="2" t="inlineStr">
+        <is>
+          <t>Language Understanding &gt; 4 Experiments &gt; 4.2 SQuAD v1.1</t>
+        </is>
+      </c>
+      <c r="M310" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rst ﬁne-tuning on TriviaQA (Joshi
+et al., 2017) befor ﬁne-tuning on SQuAD.
+Our best performing system outperforms the top leaderboard system by +1.5 F1 in ensembling and +1.3 F1 as a single system. In fact, our single BERT model outperforms the top </t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>f1-q6</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>How many total parameters does BERT-large have?</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>total parameters=340m</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J311" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K311" s="2" t="inlineStr">
+        <is>
+          <t>acl-n19-1423-bert.pdf</t>
+        </is>
+      </c>
+      <c r="L311" s="2" t="inlineStr">
+        <is>
+          <t>Language Understanding &gt; 5 Ablation Studies &gt; 5.2 Effect of Model Size</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="inlineStr">
+        <is>
+          <t>e literature is (L=64, H=512, A=2) with 235M parameters (Al-Rfou et al., 2018). 
+By contrast, BERTBASE contains 110M parameters and BERTLARGE contains 340M parameters.
+It has long been known that increasing the model size will lead to continual imp</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>f1-q7</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>How many GPUs were used to train GPT-4?</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>unanswerable</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>(not in source)</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="n"/>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J312" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K312" s="2" t="inlineStr">
+        <is>
+          <t>acl-n19-1423-bert.pdf</t>
+        </is>
+      </c>
+      <c r="L312" s="2" t="inlineStr">
+        <is>
+          <t>Language Understanding &gt; 5 Ablation Studies &gt; 5.2 Effect of Model Size</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="inlineStr">
+        <is>
+          <t>Results on selected GLUE tasks are shown in Table 6. In this table, we report the average Dev Set accuracy from 5 random restarts of ﬁne-tuning. We can see that larger models lead to a strict accuracy improvement across all four datasets, even for MR</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>f2-q1</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>What was real median household income in the United States in 2022?</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>$74,580</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K313" s="2" t="inlineStr">
+        <is>
+          <t>census-p60-279.pdf</t>
+        </is>
+      </c>
+      <c r="L313" s="2" t="inlineStr">
+        <is>
+          <t>Income in the United States: 2022 &gt; HOUSEHOLD INCOME BY SELECTED CHARACTERISTICS &gt; All Households</t>
+        </is>
+      </c>
+      <c r="M313" s="2" t="inlineStr">
+        <is>
+          <t>All Households
+Real median household income 
+was $74,580 in 2022, 2.3 percent 
+lower than the 2021 estimate of 
+$76,330. It was 4.7 percent lower 
+than the 2019 median, the year 
+before the start of the COVID-19 
+pandemic and the corresponding 
+rece</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>f2-q2</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>By how much did real median household income change between 2021 and 2022?</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>2.3 percent</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J314" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K314" s="2" t="inlineStr">
+        <is>
+          <t>census-p60-279.pdf</t>
+        </is>
+      </c>
+      <c r="L314" s="2" t="inlineStr">
+        <is>
+          <t>Income in the United States: 2022 &gt; HOUSEHOLD INCOME BY SELECTED CHARACTERISTICS &gt; Change: 2021 to 2022
+2022 Median Income</t>
+        </is>
+      </c>
+      <c r="M314" s="2" t="inlineStr">
+        <is>
+          <t>Change: 2021 to 2022
+2022 Median Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>f2-q3</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>How did the money income Gini index change between 2021 and 2022?</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>from 0.494 to 0.488</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J315" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K315" s="2" t="inlineStr">
+        <is>
+          <t>census-p60-279.pdf</t>
+        </is>
+      </c>
+      <c r="L315" s="2" t="inlineStr">
+        <is>
+          <t>Income in the United States: 2022 &gt; HOUSEHOLD INCOME BY SELECTED CHARACTERISTICS &gt; Money Income Inequality27</t>
+        </is>
+      </c>
+      <c r="M315" s="2" t="inlineStr">
+        <is>
+          <t>Money Income Inequality27
+The Gini index is a statistical measure of income inequality ranging 
+from 0.0 to 1.0. It measures the 
+amount that any two incomes 
+differ, on average, relative to 
+mean income. It is an indicator 
+of how far apart or “spr</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>f2-q4</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>What was the median income of married-couple households in 2022 according to Table A-1?</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>married-couple + 110,800</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J316" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K316" s="2" t="inlineStr">
+        <is>
+          <t>census-p60-279.pdf</t>
+        </is>
+      </c>
+      <c r="L316" s="2" t="inlineStr">
+        <is>
+          <t>Income in the United States: 2022 &gt; HOUSEHOLD INCOME BY SELECTED CHARACTERISTICS &gt; Type of Household8</t>
+        </is>
+      </c>
+      <c r="M316" s="2" t="inlineStr">
+        <is>
+          <t>Type of Household8
+The 2022 real median income of 
+family households declined by 
+2.9 percent from 2021, and the 
+real median income of married-couple families declined by 3.9 
+percent. Among family households, married couples had the 
+highest media</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>f2-q5</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>What was the median income of family households in 2022 according to Table A-1?</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr">
+        <is>
+          <t>family households + 95,450</t>
+        </is>
+      </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J317" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K317" s="2" t="inlineStr">
+        <is>
+          <t>census-p60-279.pdf</t>
+        </is>
+      </c>
+      <c r="L317" s="2" t="inlineStr">
+        <is>
+          <t>Income in the United States: 2022 &gt; HOUSEHOLD INCOME BY SELECTED CHARACTERISTICS &gt; Type of Household8</t>
+        </is>
+      </c>
+      <c r="M317" s="2" t="inlineStr">
+        <is>
+          <t>Type of Household8
+The 2022 real median income of 
+family households declined by 
+2.9 percent from 2021, and the 
+real median income of married-couple families declined by 3.9 
+percent. Among family households, married couples had the 
+highest media</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>f2-q6</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>What was the median income of nonfamily households in 2022 according to Table A-1?</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>nonfamily households + 45,440</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J318" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K318" s="2" t="inlineStr">
+        <is>
+          <t>census-p60-279.pdf</t>
+        </is>
+      </c>
+      <c r="L318" s="2" t="inlineStr">
+        <is>
+          <t>Income in the United States: 2022 &gt; HOUSEHOLD INCOME BY SELECTED CHARACTERISTICS &gt; Type of Household8</t>
+        </is>
+      </c>
+      <c r="M318" s="2" t="inlineStr">
+        <is>
+          <t>an 
+income between these groups and 
+non-Hispanic White households 
+decreased.12
+Nonfamily households had a 
+median income of $45,440 in 
+2022, which was not significantly 
+different from 2021 (Figure 1 and 
+Table A-1). Nonfamily households with a f</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>f2-q7</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>What was the median household income in Canada in 2022?</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>unanswerable</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>(not in source)</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="n"/>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J319" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K319" s="2" t="inlineStr">
+        <is>
+          <t>census-p60-279.pdf</t>
+        </is>
+      </c>
+      <c r="L319" s="2" t="inlineStr">
+        <is>
+          <t>Income in the United States: 2022 &gt; HOUSEHOLD INCOME BY SELECTED CHARACTERISTICS &gt; All Households</t>
+        </is>
+      </c>
+      <c r="M319" s="2" t="inlineStr">
+        <is>
+          <t>All Households
+Real median household income 
+was $74,580 in 2022, 2.3 percent 
+lower than the 2021 estimate of 
+$76,330. It was 4.7 percent lower 
+than the 2019 median, the year 
+before the start of the COVID-19 
+pandemic and the corresponding 
+rece</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>f3-q1</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>How many television pictures does Part III of the Surveyor VI report present?</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>139 of the total number</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J320" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K320" s="2" t="inlineStr">
+        <is>
+          <t>surveyor-vi-tv-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L320" s="2" t="inlineStr"/>
+      <c r="M320" s="2" t="inlineStr">
+        <is>
+          <t>ists of selected pictures from Surveyor VI and appropriate explanatory material.
+This Part III presents 139 of the total number of television pictures transmitted to earth from the lunar surface, between November 10 and November 24, 1967; 46 mosaics</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>f3-q2</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>Between which dates were the Surveyor VI television pictures transmitted?</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr">
+        <is>
+          <t>november 10 and november 24, 1967</t>
+        </is>
+      </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J321" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K321" s="2" t="inlineStr">
+        <is>
+          <t>surveyor-vi-tv-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L321" s="2" t="inlineStr"/>
+      <c r="M321" s="2" t="inlineStr">
+        <is>
+          <t>ists of selected pictures from Surveyor VI and appropriate explanatory material.
+This Part III presents 139 of the total number of television pictures transmitted to earth from the lunar surface, between November 10 and November 24, 1967; 46 mosaics</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>f3-q3</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>How many mosaics are included in Part III?</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>46 mosaics</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J322" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K322" s="2" t="inlineStr">
+        <is>
+          <t>surveyor-vi-tv-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L322" s="2" t="inlineStr"/>
+      <c r="M322" s="2" t="inlineStr">
+        <is>
+          <t>ists of selected pictures from Surveyor VI and appropriate explanatory material.
+This Part III presents 139 of the total number of television pictures transmitted to earth from the lunar surface, between November 10 and November 24, 1967; 46 mosaics</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>f3-q4</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>What is the mass of the Surveyor survey TV camera?</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>7.3-kg camera</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J323" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K323" s="2" t="inlineStr">
+        <is>
+          <t>surveyor-vi-tv-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L323" s="2" t="inlineStr"/>
+      <c r="M323" s="2" t="inlineStr">
+        <is>
+          <t>Il. Television Subsystem M. I. Smokler
+The Surveyor TV system is designed to obtain video pictures of the lunar surface, lunar sky, and portions of the landed spacecraft. It includes a survey camera capable of panoramic viewing, and a TV auxiliary t</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>f3-q5</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>Over what range can the Surveyor TV camera focus?</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>1.22 m to infinity</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J324" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K324" s="2" t="inlineStr">
+        <is>
+          <t>surveyor-vi-tv-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L324" s="2" t="inlineStr"/>
+      <c r="M324" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> was capable of providing either a
+Fig. II-5. Variable-focal-length lens assembly
+100-mm or 25-mm focal length, resulting in a vertical field of view of approximately 6.43 or 25.3 deg, respectively, as measured by the angular subtense of the vertic</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>f3-q6</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>What scene luminance range is the Surveyor camera designed to accommodate?</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>0.008 to 2600 ft-l</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J325" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K325" s="2" t="inlineStr">
+        <is>
+          <t>surveyor-vi-tv-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L325" s="2" t="inlineStr"/>
+      <c r="M325" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tification signals and to provide appropriate video mixing.
+A. Camera Description
+The slow-scan survey TV camera, shown in Figs. II-1 and II-2, provides images of the lunar surface over a 360-deg panorama. Each picture, or frame, is imaged through </t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>f3-q7</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>Which mission number in the Surveyor series was Surveyor VI?</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>the sixth in a series of unmanned lunar soft-landing missions</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J326" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K326" s="2" t="inlineStr">
+        <is>
+          <t>surveyor-vi-tv-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L326" s="2" t="inlineStr"/>
+      <c r="M326" s="2" t="inlineStr">
+        <is>
+          <t>Preface
+This three-part document constitutes the Project Mission Report on Surveyor VI, the sixth in a series of unmanned lunar soft-landing missions.
+Part I of this Technical Report consists of a technical description and an evaluation of engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>f3-q8</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>What was the landing site latitude of Surveyor VII?</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>unanswerable</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr">
+        <is>
+          <t>(not in source)</t>
+        </is>
+      </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="n"/>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J327" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K327" s="2" t="inlineStr">
+        <is>
+          <t>surveyor-vi-tv-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L327" s="2" t="inlineStr"/>
+      <c r="M327" s="2" t="inlineStr">
+        <is>
+          <t>Preface
+This three-part document constitutes the Project Mission Report on Surveyor VI, the sixth in a series of unmanned lunar soft-landing missions.
+Part I of this Technical Report consists of a technical description and an evaluation of engineer</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>f2-q9</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>According to Table A-2, what was the median household income for all races in 2015, in 2022 dollars?</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>2015 + 68,410</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="n"/>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J328" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K328" s="2" t="inlineStr">
+        <is>
+          <t>census-p60-279.pdf</t>
+        </is>
+      </c>
+      <c r="L328" s="2" t="inlineStr">
+        <is>
+          <t>Income in the United States: 2022 &gt; HOUSEHOLD INCOME BY SELECTED CHARACTERISTICS &gt; All Households</t>
+        </is>
+      </c>
+      <c r="M328" s="2" t="inlineStr">
+        <is>
+          <t>All Households
+Real median household income 
+was $74,580 in 2022, 2.3 percent 
+lower than the 2021 estimate of 
+$76,330. It was 4.7 percent lower 
+than the 2019 median, the year 
+before the start of the COVID-19 
+pandemic and the corresponding 
+rece</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>f2-q10</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>According to Table A-2, what was the mean household income for all races in 1990, in 2022 dollars?</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>1990 + 76,820</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="n"/>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K329" s="2" t="inlineStr">
+        <is>
+          <t>census-p60-279.pdf</t>
+        </is>
+      </c>
+      <c r="L329" s="2" t="inlineStr">
+        <is>
+          <t>Income in the United States: 2022 &gt; APPENDIX A. ESTIMATES OF INCOME &gt; Endnotes</t>
+        </is>
+      </c>
+      <c r="M329" s="2" t="inlineStr">
+        <is>
+          <t>Table A-2. Households by Total Money Income, Race, and Hispanic Origin of Householder: 1967 to 2022—Con. (Income in 2022 dollars, adjusted using the C-CPI-U (2000–2022) and R-CPI-U-RS (pre-2000). Households as of March of the following year. Informat</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>f4-q1</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>Combien de décès dus aux maladies de l'appareil circulatoire pour 100 000 habitants l'UE-28 comptait-elle en 2015 ?</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="n"/>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J330" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K330" s="2" t="inlineStr">
+        <is>
+          <t>eurostat-chiffres-cles-2019-fr.pdf</t>
+        </is>
+      </c>
+      <c r="L330" s="2" t="inlineStr">
+        <is>
+          <t>Santé &gt; Décès causés par des maladies de l’appareil circulatoire (taux de mortalité standardisé pour 100 000 habitants par sexe, 2015)</t>
+        </is>
+      </c>
+      <c r="M330" s="2" t="inlineStr">
+        <is>
+          <t>1 500
+1 400
+1 300
+1 200
+1 100
+1 000
+900
+800
+700
+600
+500
+400
+300
+200
+100</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>f4-q2</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>En 2015, combien de fois plus de risques de mourir d'une maladie de l'appareil circulatoire avait une personne vivant en Bulgarie qu'une personne vivant en France ?</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>5,5 fois</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K331" s="2" t="inlineStr">
+        <is>
+          <t>eurostat-chiffres-cles-2019-fr.pdf</t>
+        </is>
+      </c>
+      <c r="L331" s="2" t="inlineStr">
+        <is>
+          <t>Santé &gt; Hommes Les deux sexes Femmes</t>
+        </is>
+      </c>
+      <c r="M331" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alors que les maladies de l’appareil circulatoire sont la première cause 
+de décès au sein de l’UE‑28, d’importantes différences s’observaient 
+entre les États membres de l’Union. Par exemple, en 2015, une personne 
+vivant en Bulgarie avait 5,5 fois </t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>f4-q3</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>Quelle part des marchandises transportées dans l'UE-28 l'est par la route ?</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>77 % + par la route</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J332" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K332" s="2" t="inlineStr">
+        <is>
+          <t>eurostat-chiffres-cles-2019-fr.pdf</t>
+        </is>
+      </c>
+      <c r="L332" s="2" t="inlineStr">
+        <is>
+          <t>Transport &gt; Chiffres clés sur l’Europe – Édition 2019  53</t>
+        </is>
+      </c>
+      <c r="M332" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">|  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  | 77 % des marchandises transportées dans l’UE-28 par la route |  |  |  |  |  |  |  |  |  |  |  |  |  |  |  |
+| --- | --- | --- | --- | --- | --- | </t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>f4-q4</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>De combien les émissions de gaz à effet de serre de l'UE-28 ont-elles baissé par rapport à 1990 ?</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>22 % + par rapport à 1990</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="n"/>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J333" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K333" s="2" t="inlineStr">
+        <is>
+          <t>eurostat-chiffres-cles-2019-fr.pdf</t>
+        </is>
+      </c>
+      <c r="L333" s="2" t="inlineStr">
+        <is>
+          <t>Environnement &gt; dans l’UE‑28 2,4 % du PIB</t>
+        </is>
+      </c>
+      <c r="M333" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2,7 BG, MT, PL
+L’indicateur relatif aux émissions de gaz à effet de serre retrace l’évolution des émissions d’origine 
+humaine pour le panier de gaz à effet de serre du protocole de Kyoto. L’UE s’est engagée à réduire la 
+quantité de gaz à effet de </t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>f5-q1</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>Who prepared the compilation of the 1950 water-use estimates in USGS Circular 115?</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>MacKichan</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J334" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K334" s="2" t="inlineStr">
+        <is>
+          <t>usgs-circ115-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L334" s="2" t="inlineStr"/>
+      <c r="M334" s="2" t="inlineStr">
+        <is>
+          <t>information available, the estimates in this report are, in general, rough approximations of the quantity of water used. The estimate for municipal use is probably the most accurrate and that for industrial surface water use the least accurate. It is</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>f5-q2</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>According to Table 1 of USGS Circular 115, how much surface water did municipalities in Illinois use in 1950 (mgd)?</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>Illinois + 1,070</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="n"/>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J335" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K335" s="2" t="inlineStr">
+        <is>
+          <t>usgs-circ115-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L335" s="2" t="inlineStr"/>
+      <c r="M335" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+during 1950 is given in table 1 and is shown graphically in figures 2 to 6. The estimates are for the five types of uses by States and by source of supply, ground water or surface water.
+MUNICIPAL USE
+Municipal water systems served 93.5 million </t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>f5-q3</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>According to Table 1 of USGS Circular 115, how much ground water did municipalities in Kansas use in 1950 (mgd)?</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>Kansas + 75</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I336" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J336" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K336" s="2" t="inlineStr">
+        <is>
+          <t>usgs-circ115-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L336" s="2" t="inlineStr"/>
+      <c r="M336" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+during 1950 is given in table 1 and is shown graphically in figures 2 to 6. The estimates are for the five types of uses by States and by source of supply, ground water or surface water.
+MUNICIPAL USE
+Municipal water systems served 93.5 million </t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>f6-q1</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>What is the word limit for section A3.2, on tackling potholes, in the DfT highways maintenance transparency report template?</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>tackle potholes + 250 words</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="n"/>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J337" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K337" s="2" t="inlineStr">
+        <is>
+          <t>dft-highways-maintenance-report-template.docx</t>
+        </is>
+      </c>
+      <c r="L337" s="2" t="inlineStr">
+        <is>
+          <t>How we maintain local roads, pavements, and the wider highway network in [LHA name] &gt; A3 – What we are doing about potholes and other road defects</t>
+        </is>
+      </c>
+      <c r="M337" s="2" t="inlineStr">
+        <is>
+          <t>ions which mean that not all defects can be resolved permanently the first time.
+Word limit – 250 words
+A3.3. How members of public can report potholes and other highway defects
+Guidance - Please set out how the public can report potholes and othe</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>f6-q2</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>Into which asset categories does table A4.1 of the DfT template break down spending on highways maintenance?</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>street lighting + drainage</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K338" s="2" t="inlineStr">
+        <is>
+          <t>dft-highways-maintenance-report-template.docx</t>
+        </is>
+      </c>
+      <c r="L338" s="2" t="inlineStr">
+        <is>
+          <t>How we maintain local roads, pavements, and the wider highway network in [LHA name] &gt; A4 – What we spend to maintain the highway network and where the funding is coming from</t>
+        </is>
+      </c>
+      <c r="M338" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A4 – What we spend to maintain the highway network and where the funding is coming from
+A4.1. – Spending on highways maintenance
+|  | 2024-25 | 2025-26 | 2026-27 (projected) |
+| --- | --- | --- | --- |
+| Total spend on highways maintenance | £ | £ </t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>f7-q1</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>In the Prevent risk assessment example matrix, what score range counts as medium risk?</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>medium risk + 7 to 11</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K339" s="2" t="inlineStr">
+        <is>
+          <t>prevent-risk-assessment-slides.pptx</t>
+        </is>
+      </c>
+      <c r="L339" s="2" t="inlineStr"/>
+      <c r="M339" s="2" t="inlineStr">
+        <is>
+          <t>An example of a risk assessment matrix
+| Low risk | 1 to 6 |
+| --- | --- |
+| Medium risk | 7 to 11 |
+| High risk | 12 + |
+| Probability | Rating | Severity of impact | Rating |
+| --- | --- | --- | --- |
+| Almost certain | 5 | Catastrophic | 5 |
+| V</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>f7-q2</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>In the Prevent risk assessment matrix, which severity of impact has the same rating as a 'Very likely' probability?</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>very likely + major</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K340" s="2" t="inlineStr">
+        <is>
+          <t>prevent-risk-assessment-slides.pptx</t>
+        </is>
+      </c>
+      <c r="L340" s="2" t="inlineStr"/>
+      <c r="M340" s="2" t="inlineStr">
+        <is>
+          <t>An example of a risk assessment matrix
+| Low risk | 1 to 6 |
+| --- | --- |
+| Medium risk | 7 to 11 |
+| High risk | 12 + |
+| Probability | Rating | Severity of impact | Rating |
+| --- | --- | --- | --- |
+| Almost certain | 5 | Catastrophic | 5 |
+| V</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>f7-q3</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>According to the Prevent slides, on what scale are the severity and likelihood of risks usually ranked?</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>1-5 scale</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K341" s="2" t="inlineStr">
+        <is>
+          <t>prevent-risk-assessment-slides.pptx</t>
+        </is>
+      </c>
+      <c r="L341" s="2" t="inlineStr"/>
+      <c r="M341" s="2" t="inlineStr">
+        <is>
+          <t>An example of a risk assessment matrix
+| Low risk | 1 to 6 |
+| --- | --- |
+| Medium risk | 7 to 11 |
+| High risk | 12 + |
+| Probability | Rating | Severity of impact | Rating |
+| --- | --- | --- | --- |
+| Almost certain | 5 | Catastrophic | 5 |
+| V</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>f7-q4</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>What score marks a critical risk in the Prevent risk assessment matrix?</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>unanswerable</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>(not in source)</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="n"/>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K342" s="2" t="inlineStr">
+        <is>
+          <t>prevent-risk-assessment-slides.pptx</t>
+        </is>
+      </c>
+      <c r="L342" s="2" t="inlineStr"/>
+      <c r="M342" s="2" t="inlineStr">
+        <is>
+          <t>An example of a risk assessment matrix
+| Low risk | 1 to 6 |
+| --- | --- |
+| Medium risk | 7 to 11 |
+| High risk | 12 + |
+| Probability | Rating | Severity of impact | Rating |
+| --- | --- | --- | --- |
+| Almost certain | 5 | Catastrophic | 5 |
+| V</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>f5-q4</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>How much water did Alaska withdraw for irrigation in 1950 according to USGS Circular 115?</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>unanswerable</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>(not in source)</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="n"/>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K343" s="2" t="inlineStr">
+        <is>
+          <t>usgs-circ115-scan.pdf</t>
+        </is>
+      </c>
+      <c r="L343" s="2" t="inlineStr"/>
+      <c r="M343" s="2" t="inlineStr">
+        <is>
+          <t>TABLE 1.--ESTIMATED WITHDRAWAL USE OF WATER IN THE UNITED STATES, 1950
+Rural 1/ Municipal Industrial 2/ Irrigational For water-
+State (1,000 acre-feet power (1,000 Ground water/Surface water}/Ground water|Surface water|Ground water|Surface water Gro</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>f4-q5</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>Quel était le taux de chômage au Japon en 2018 selon ce rapport ?</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>unanswerable</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>(not in source)</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="n"/>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J344" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K344" s="2" t="inlineStr">
+        <is>
+          <t>eurostat-chiffres-cles-2019-fr.pdf</t>
+        </is>
+      </c>
+      <c r="L344" s="2" t="inlineStr">
+        <is>
+          <t>Marché du travail &gt; Taux de chômage 
+(part en pourcentage de la population active âgée de 15 à 74 ans, 2018)</t>
+        </is>
+      </c>
+      <c r="M344" s="2" t="inlineStr">
+        <is>
+          <t>Taux de chômage 
+(part en pourcentage de la population active âgée de 15 à 74 ans, 2018)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26315,7 +31068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -29029,54 +33782,1429 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="n"/>
-      <c r="G50" s="2" t="n"/>
-      <c r="H50" s="2" t="n"/>
-      <c r="I50" s="2" t="n"/>
-      <c r="J50" s="2" t="n"/>
-      <c r="K50" s="2" t="n"/>
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>f1-q1</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>What are the layer, hidden size and attention head settings of BERT-base?</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>12 layers, hidden size 768, 12 attention heads (110M parameters).</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>BERT-base has 12 layers (L), a hidden size (H) of 768, and 12 attention heads (A) [S2].</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>States L=12, H=768, A=12.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0.0007107</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>f1-q4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Which corpora were used to pre-train BERT?</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>BooksCorpus (800M words) and English Wikipedia (2,500M words).</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>The BooksCorpus (800M words) and English Wikipedia (2,500M words) were used to pre-train BERT [S1].</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>BooksCorpus 800M and English Wikipedia 2,500M words.</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>0.0003391</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>f2-q1</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>What was real median household income in the United States in 2022?</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>$74,580</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Real median household income in the United States was $74,580 in 2022 [S1].</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0.0006071</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>f2-q4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>What was the median income of married-couple households in 2022 according to Table A-1?</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>$110,800</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>The median income of married-couple households in 2022 was $110,800 [S2].</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0.0008223</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>f2-q6</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>What was the median income of nonfamily households in 2022 according to Table A-1?</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>$45,440</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>The median income of nonfamily households in 2022 was $45,440 [S1, S4].</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0.0007861</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>f3-q1</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>How many television pictures does Part III of the Surveyor VI report present?</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>139 pictures.</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Part III of the Surveyor VI report presents 139 television pictures [S1, S2]. It also includes 46 mosaics composed of individual frames [S1].</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>139 pictures, as the reference.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0.0004818</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>f3-q4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>What is the mass of the Surveyor survey TV camera?</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>7.3 kg.</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>The Surveyor survey TV camera has a mass of 7.3 kg [S3].</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0.000513</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>f3-q8</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>What was the landing site latitude of Surveyor VII?</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Not stated in the source.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_EVIDENCE. The provided documents discuss the Surveyor VI mission but do not contain any information about the landing site latitude of Surveyor VII [S1, S2, S3, S4, S5].</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>correct-abstain</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Declined; not in the source.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>No answer to support.</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>0.0004891</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>f2-q9</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>According to Table A-2, what was the median household income for all races in 2015, in 2022 dollars?</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>$68,410</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_EVIDENCE. The provided text includes Table A-2, but it only contains data for the years 2019, 2020, 2021, and 2022. Information for 2015 is not available in the given table [S2].</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>wrong-abstain</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Declined; the Table A-2 2015 row is in the index (correct, read row by row) but not in the top 5, which held the 2019-2022 rows.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>No answer to support.</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0.0010577</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>f2-q10</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>According to Table A-2, what was the mean household income for all races in 1990, in 2022 dollars?</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>$76,820</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_EVIDENCE. The provided tables do not contain data for the year 1990 for "ALL RACES" [S2, S3, S4].</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>wrong-abstain</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Declined; the 1990 row is in the index but not in the top 5.</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>No answer to support.</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0.0014733</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>f4-q1</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Combien de décès dus aux maladies de l'appareil circulatoire pour 100 000 habitants l'UE-28 comptait-elle en 2015 ?</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>381 décès pour 100 000 habitants</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_EVIDENCE. Les documents fournis ne contiennent pas le nombre de décès dus aux maladies de l'appareil circulatoire pour 100 000 habitants dans l'UE-28 en 2015. Ils mentionnent seulement le titre d'une section et des chiffres qui ne sont pas clairement associés à cette statistique [S1, S2, S3, S4].</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>wrong-abstain</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Declined; the chart callout '381 deces' is not in the index (chart read as an empty table).</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>No answer to support.</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>0.001013</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>f4-q2</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>En 2015, combien de fois plus de risques de mourir d'une maladie de l'appareil circulatoire avait une personne vivant en Bulgarie qu'une personne vivant en France ?</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>5,5 fois plus</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>En 2015, une personne vivant en Bulgarie avait 5,5 fois plus de risques de mourir d'une maladie de l'appareil circulatoire qu'une personne vivant en France [S1].</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>5,5 fois, as the reference.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0.0007765</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>f4-q3</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Quelle part des marchandises transportées dans l'UE-28 l'est par la route ?</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>77 %</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>77 % des marchandises transportées dans l'UE-28 le sont par la route [S1, S2, S3, S4].</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>77 %, as the reference.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>0.0010076</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>f4-q4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>De combien les émissions de gaz à effet de serre de l'UE-28 ont-elles baissé par rapport à 1990 ?</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>De 22 % par rapport à 1990</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>En 2016, les émissions de gaz à effet de serre de l'UE-28 avaient baissé de 22,4 % par rapport à leurs niveaux de 1990 [S1].</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>22,4 % against 1990 (the prose figure; the chart callout rounds it to 22 %).</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>The cited chunk states 22,4 % against 1990; the reference phrase was the rounded callout.</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>0.0007475</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>f5-q1</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Who prepared the compilation of the 1950 water-use estimates in USGS Circular 115?</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Kenneth A. MacKichan</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Kenneth A. MacKichan prepared the compilation of the 1950 water-use estimates in USGS Circular 115 [S1, S3].</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Matches the reference answer.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0.0006547</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>f5-q2</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>According to Table 1 of USGS Circular 115, how much surface water did municipalities in Illinois use in 1950 (mgd)?</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>1,070 mgd</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_EVIDENCE. The provided text includes Table 1, which lists municipal water usage for several states, but Illinois is not among them [S3].</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>wrong-abstain</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Declined; the OCR row 'Illinois ... 1,070' is in the index but not in the top 5.</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>No answer to support.</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>0.0006794</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>f5-q3</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>According to Table 1 of USGS Circular 115, how much ground water did municipalities in Kansas use in 1950 (mgd)?</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>75 mgd</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_EVIDENCE. The provided text includes Table 1, but Kansas is not listed in the table [S2].</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>wrong-abstain</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Declined; the Kansas row is not in the top 5, and OCR reads its 75 as 78.</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>No answer to support.</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0.0006727</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>f6-q1</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>What is the word limit for section A3.2, on tackling potholes, in the DfT highways maintenance transparency report template?</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>250 words</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_EVIDENCE. The provided text describes section A3.2 and its guidance, but it does not explicitly state a word limit for this specific section [S1, S3, S4].</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>wrong-abstain</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Declined; the rank-1 chunk has 'Word limit - 250 words' but the A3.2 heading is in an earlier chunk, so the model could not tie the limit to A3.2.</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>No answer to support.</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>0.0006455</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>f6-q2</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Into which asset categories does table A4.1 of the DfT template break down spending on highways maintenance?</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Carriageways, footways, structures, drainage, street lighting and other assets</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Table A4.1 of the DfT template breaks down spending on highways maintenance into the following asset categories: Carriageways, Footways, Structures (for example bridges or tunnels), Drainage, Street lighting, and Other assets [S1].</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>All six categories.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>0.0006089999999999999</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>f7-q1</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>In the Prevent risk assessment example matrix, what score range counts as medium risk?</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>7 to 11</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>In the Prevent risk assessment example matrix, a score range of 7 to 11 counts as medium risk [S1].</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>7 to 11, from the slide table.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>0.000335</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>f7-q2</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>In the Prevent risk assessment matrix, which severity of impact has the same rating as a 'Very likely' probability?</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Major (rating 4)</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>The severity of impact that has the same rating as a 'Very likely' probability is 'Major' [S1]. Both have a rating of 4 [S1].</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Major, rating 4, from the slide table.</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>0.0003734</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>f7-q3</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>According to the Prevent slides, on what scale are the severity and likelihood of risks usually ranked?</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>A 1-5 scale</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>The severity and likelihood of risks are usually ranked on a 1-5 scale [S3].</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>1-5 scale, from the slide table.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>A source the answer names contains the expected phrase.</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>0.0003761</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>f7-q4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>What score marks a critical risk in the Prevent risk assessment matrix?</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Not stated in the source (the highest band is High risk, 12+).</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_EVIDENCE. The provided text describes risk levels as low, medium, and high, but does not define a "critical risk" or specify a score for it [S1].</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>correct-abstain</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Declined; the matrix has no critical band.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>No answer to support.</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0.0003338</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>f5-q4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>How much water did Alaska withdraw for irrigation in 1950 according to USGS Circular 115?</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Not stated in the source.</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_EVIDENCE. The provided text does not contain information about the amount of water Alaska withdrew for irrigation in 1950. While Table 1 lists water withdrawal data for various states, Alaska is not included in the table [S1].</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>correct-abstain</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Declined; Alaska is not in Table 1.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>No answer to support.</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>0.000753</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>f4-q5</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Quel était le taux de chômage au Japon en 2018 selon ce rapport ?</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Not stated in the source.</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_EVIDENCE. Le rapport ne mentionne pas le taux de chômage au Japon en 2018 [S1, S2, S3, S4, S5].</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>correct-abstain</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Declined; not in the report.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>No answer to support.</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>0.0006146</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="n"/>
+      <c r="G75" s="2" t="n"/>
+      <c r="H75" s="2" t="n"/>
+      <c r="I75" s="2" t="n"/>
+      <c r="J75" s="2" t="n"/>
+      <c r="K75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
           <t>Total answer cost (USD)</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr"/>
-      <c r="C51" s="2" t="inlineStr"/>
-      <c r="D51" s="2" t="inlineStr"/>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="2">
-        <f>SUM(K2:K49)</f>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2">
+        <f>SUM(K2:K74)</f>
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Labels: correct, correct-abstain, partial, wrong, wrong-abstain. Scored blind by Claude with the spec 0004 rubric; rounds were hidden as X/Y. A1 (after the fixes) was scored with the same rubric against the references, not blind.</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
-      <c r="G52" s="2" t="n"/>
-      <c r="H52" s="2" t="n"/>
-      <c r="I52" s="2" t="n"/>
-      <c r="J52" s="2" t="n"/>
-      <c r="K52" s="2" t="n"/>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Labels: correct, correct-abstain, partial, wrong, wrong-abstain. Scored blind by Claude with the spec 0004 rubric; rounds were hidden as X/Y. A1 (after the fixes) and A2 (extractor v4) were scored with the same rubric against the references, not blind.</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="n"/>
+      <c r="F77" s="2" t="n"/>
+      <c r="G77" s="2" t="n"/>
+      <c r="H77" s="2" t="n"/>
+      <c r="I77" s="2" t="n"/>
+      <c r="J77" s="2" t="n"/>
+      <c r="K77" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
